--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0002.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0002.xlsx
@@ -8504,7 +8504,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Hồi 3: Cooldown chiêu Impulse Tide giảm.</t>
+          <t>Hồi 3: Thời gian hồi chiêu Impulse Tide giảm.</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Hồi 3: Cooldown chiêu &lt;color=Highlight&gt;Echo Skill&lt;/color&gt; giảm 85%.</t>
+          <t>Hồi 3: Thời gian hồi chiêu &lt;color=Highlight&gt;Echo Skill&lt;/color&gt; giảm 85%.</t>
         </is>
       </c>
     </row>
@@ -17734,7 +17734,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Thật khó để tìm thấy Cộng Hưởng&lt;/i&gt;</t>
+          <t>&lt;i&gt;Cộng hưởng thật khó tìm...&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -17800,7 +17800,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Tần số của cậu chẳng nổi bật gì giữa Resonators.
+          <t>Tần số của cậu chẳng nổi bật gì giữa các Resonator.
 Nhưng sức mạnh tưởng như nhỏ bé ấy lại đủ sức vượt qua cả ngọn lửa rèn và những nhát búa.</t>
         </is>
       </c>
@@ -17866,7 +17866,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Một cơ quan hoạt động độc lập với các nhánh hành pháp, tư pháp và quân sự của Huanglong, đứng đầu là "Chỉ Huy Trưởng". Trực thuộc Hoàng đế Huanglong, cơ quan này có quyền điều tra bất kỳ vụ án, quan chức hay tội phạm nào mà không cần sự chấp thuận của các cơ quan khác, với quyền "hành động trước, báo cáo sau". Đảm nhiệm xử lý các vụ án phức tạp quanh năm, cơ quan này đã phát triển chuyên môn đặc biệt trong việc quản lý Resonators.</t>
+          <t>Một cơ quan hoạt động độc lập với các nhánh hành pháp, tư pháp và quân sự của Huanglong, đứng đầu là "Chỉ Huy Trưởng". Trực thuộc Hoàng đế Huanglong, cơ quan này có quyền điều tra bất kỳ vụ án, quan chức hay tội phạm nào mà không cần sự chấp thuận của các cơ quan khác, với quyền "hành động trước, báo cáo sau". Đảm nhiệm xử lý các vụ án phức tạp quanh năm, cơ quan này đã phát triển chuyên môn đặc biệt trong việc quản lý Resonator.</t>
         </is>
       </c>
     </row>
@@ -17931,7 +17931,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Một cơ quan đặc biệt chịu trách nhiệm giám sát các Sentinel, thiên văn và lịch pháp tại các thành phố trên khắp Huanglong. Dưới sự lãnh đạo của Bộ trưởng Bộ Sự vụ Sentinel tại Mingting, cơ quan này có các chi nhánh trực thuộc tại sáu thành phố khác, mỗi nơi do một Supervisor đứng đầu. Dù có quyền tự chủ trong các vấn đề liên quan đến Sentinel, họ chỉ được phép tư vấn và giám sát các cơ quan hành chính của từng thành phố và Mingting.</t>
+          <t>Một cơ quan đặc biệt chịu trách nhiệm giám sát các Sentinel, thiên văn và lịch pháp tại các thành phố trên khắp Huanglong. Dưới sự lãnh đạo của Bộ trưởng Bộ Sự vụ Sentinel tại Mingting, cơ quan này có các chi nhánh trực thuộc tại sáu thành phố khác, mỗi nơi do một Giám sát viên đứng đầu. Dù có quyền tự chủ trong các vấn đề liên quan đến Sentinel, họ chỉ được phép tư vấn và giám sát các cơ quan hành chính của từng thành phố và Mingting.</t>
         </is>
       </c>
     </row>
@@ -17996,7 +17996,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Khả năng Resonance độc đáo của Qiuyuan. Bằng cách cảm nhận bản chất và sự khác biệt của các tần số xung quanh, cậu có thể xác định vị trí kẻ địch và thậm chí cả trạng thái tâm trí của chúng. Trong trường hợp cực đoan, nhận thức này có thể được khuếch đại qua Sonoro Spheres, hiện thực hóa những hình ảnh tinh thần của kẻ địch—hoặc chính bản thân cậu.</t>
+          <t>Khả năng Cộng Hưởng độc đáo của Qiuyuan. Bằng cách cảm nhận bản chất và sự khác biệt của các tần số xung quanh, cậu có thể xác định vị trí kẻ địch và thậm chí cả trạng thái tâm trí của chúng. Trong trường hợp cực đoan, nhận thức này có thể được khuếch đại qua Sonoro Spheres, hiện thực hóa những hình ảnh tinh thần của kẻ địch—hoặc chính bản thân cậu.</t>
         </is>
       </c>
     </row>
@@ -18061,7 +18061,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Một nền văn minh nằm ở vùng cực của Solaris-3. Những biến đổi cổ xưa trong trục hành tinh đã định hình lại địa lý thế giới, biến khu vực Lahai-Roi thành cực của hành tinh như ngày nay. Theo thời gian, những hang động rộng lớn sâu dưới lớp băng tuyết dày dần trở nên có thể sinh sống được. Trong thiên đường ngầm ấm áp và ẩm ướt này, một đô thị học thuật dành cho Resonators đã mọc lên, được tôn vinh là "Thiên Đường Nghiên Cứu của Solaris" và "Utopia cho các Nhà Nghiên Cứu."</t>
+          <t>Một nền văn minh nằm ở vùng cực của Solaris-3. Những biến đổi cổ xưa trong trục hành tinh đã định hình lại địa lý thế giới, biến khu vực Lahai-Roi thành cực của hành tinh như ngày nay. Theo thời gian, những hang động rộng lớn sâu dưới lớp băng tuyết dày dần trở nên có thể sinh sống được. Trong thiên đường ngầm ấm áp và ẩm ướt này, một đô thị học thuật dành cho Resonator đã mọc lên, được tôn vinh là "Thiên Đường Nghiên Cứu của Solaris" và "Utopia cho các Nhà Nghiên Cứu."</t>
         </is>
       </c>
     </row>
@@ -18259,8 +18259,8 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Những Tacet Field tồn tại trong các chiều không gian biệt lập. 
-"Tacet Field" được cho là nơi khởi nguồn của mọi Tacet Discord. Những địa điểm này có bầu trời là biển đảo ngược và một dấu Tacet hình chữ thập sâu thẳm trên mặt đất. Âm vang tràn ngập không khí, kết nối thế giới của chúng ta với một không gian bí ẩn thông qua một sợi Resonance Cord trắng. Những khu vực này thu hút sự tụ tập của Tacet Discord.</t>
+          <t>Những Tổ Tacet tồn tại trong các chiều không gian biệt lập. 
+"Tổ Tacet" được cho là nơi khởi nguồn của mọi Tacet Discord. Những địa điểm này có bầu trời là biển đảo ngược và một dấu Tacet hình chữ thập sâu thẳm trên mặt đất. Âm vang tràn ngập không khí, kết nối thế giới của chúng ta với một không gian bí ẩn thông qua một sợi Dây Cộng Hưởng trắng. Những khu vực này thu hút sự tụ tập của Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -18325,7 +18325,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Là quan chức cao nhất trong Bộ Chiến tranh của Huanglong, Bộ trưởng giám sát tất cả các vấn đề quân sự của sáu thành phố ở Huanglong. Danh hiệu "Grand Marshal" được dùng để biểu thị cấp bậc và quyền hạn của chức vụ này.</t>
+          <t>Là quan chức cao nhất trong Bộ Chiến tranh của Huanglong, Bộ trưởng giám sát tất cả các vấn đề quân sự của sáu thành phố ở Huanglong. Danh hiệu "Đại Nguyên Soái" được dùng để biểu thị cấp bậc và quyền hạn của chức vụ này.</t>
         </is>
       </c>
     </row>
@@ -18455,7 +18455,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Ministry of War là cơ quan chỉ huy quân sự tối cao của Huanglong, đặt trụ sở tại Mingting và có chi nhánh ở cả sáu thành phố. Người đứng đầu, Bộ Trưởng Chiến Tranh, nắm quyền chỉ huy tối cao mọi vấn đề quân sự. Quyền hạn được ủy thác cho một Đại Tướng ở mỗi thành phố, phụ trách quản lý lực lượng địa phương. Dù Mingting thường bổ nhiệm các Đại Tướng này, nhưng ở một số thành phố đặc biệt, các Sentinel địa phương có quyền tự quyết.</t>
+          <t>Bộ Chiến Tranh là cơ quan chỉ huy quân sự tối cao của Huanglong, đặt trụ sở tại Mingting và có chi nhánh ở cả sáu thành phố. Người đứng đầu, Bộ Trưởng Chiến Tranh, nắm quyền chỉ huy tối cao mọi vấn đề quân sự. Quyền hạn được ủy thác cho một Đại Tướng ở mỗi thành phố, phụ trách quản lý lực lượng địa phương. Dù Mingting thường bổ nhiệm các Đại Tướng này, nhưng ở một số thành phố đặc biệt, các Sentinel địa phương có quyền tự quyết.</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Một quái vật kết hợp thường xuất hiện cùng với Void Storm. Trong những khoảng lặng giữa các cơn bão, nó chủ yếu trú ngụ tại môi trường Hư Vật cô đặc ở sa mạc Mawburrow. Các Bộ điều tiết Hư Vật trên đầu vừa là nguồn sức mạnh, vừa là điểm yếu của nó.</t>
+          <t>Một quái vật kết hợp thường xuất hiện cùng với Bão Hư Không. Trong những khoảng lặng giữa các cơn bão, nó chủ yếu trú ngụ tại môi trường Hư Vật cô đặc ở sa mạc Mawburrow. Các Bộ điều tiết Hư Vật trên đầu vừa là nguồn sức mạnh, vừa là điểm yếu của nó.</t>
         </is>
       </c>
     </row>
@@ -18782,7 +18782,7 @@
       <c r="M282" t="inlineStr">
         <is>
           <t>Được gọi chính thức là "Đơn vị Điều dưỡng Resonator", phòng khám là cơ sở kết hợp giữa lâm sàng và nghiên cứu, do Rabelle College giám sát.
-Được quản lý bởi bác sĩ của Học viện, Luuk Herssen, nơi đây sử dụng Liệu pháp Tần số để cung cấp dịch vụ chăm sóc sức khỏe toàn diện cho sinh viên và giảng viên của Startorch Academy.</t>
+Được quản lý bởi bác sĩ của Học viện, Luuk Herssen, nơi đây sử dụng Liệu pháp Tần số để cung cấp dịch vụ chăm sóc sức khỏe toàn diện cho sinh viên và giảng viên của Học viện Startorch.</t>
         </is>
       </c>
     </row>
@@ -18849,7 +18849,7 @@
       <c r="M283" t="inlineStr">
         <is>
           <t>Một thiết bị xác thực danh tính do Spacetrek Collective cấp, là trang bị an toàn bắt buộc khi di chuyển qua Lahai-Roi.
-Tất cả sinh viên năm nhất phải hoàn thành việc ghi và đăng ký Cassette dưới sự giám sát của giảng viên tại Viện Nghiên Cứu trước khi mạo hiểm ra ngoài các khu vực được bảo vệ của Học viện.</t>
+Tất cả sinh viên năm nhất phải hoàn thành việc ghi và đăng ký Cassette dưới sự giám sát của giảng viên tại Viện Nghiên cứu trước khi mạo hiểm ra ngoài các khu vực được bảo vệ của Học viện.</t>
         </is>
       </c>
     </row>
@@ -18915,7 +18915,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Terminal tiêu chuẩn cho thành viên Spacetrek Collective, được thiết kế để chứa Rabelle Cassette.
+          <t>Thiết bị đầu cuối tiêu chuẩn cho thành viên Spacetrek Collective, được thiết kế để chứa Rabelle Cassette.
 Vỏ ngoài được chế tạo từ vật liệu composite đặc biệt, mô phỏng kỹ thuật của Exostrider, giúp chống chịu một phần trước Void Storm.</t>
         </is>
       </c>
@@ -18982,7 +18982,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Một cỗ máy khổng lồ có nguồn gốc ngoài hành tinh, hiện đang ngủ yên tại vùng đất băng giá Roya. Startorch Academy được thành lập để đào tạo các Đồng Bộ Giả có khả năng thiết lập Resonance Tăng Cường với nó.
+          <t>Một cỗ máy khổng lồ có nguồn gốc ngoài hành tinh, hiện đang ngủ yên tại vùng đất băng giá Roya. Học viện Startorch được thành lập để đào tạo các Đồng Bộ Giả có khả năng thiết lập Cộng Hưởng Tăng Cường với nó.
 Trong Thần thoại Tam Vị của Roya, nó được tôn thờ là Baldur, hiện thân trần thế của thần mặt trời Sol. Truyền thuyết kể rằng nó từng dùng thanh đại kiếm chống đỡ vỏ Trái Đất sụp đổ, cứu Roya khỏi diệt vong. Lời tiên tri cho rằng nó sẽ thức tỉnh để đối đầu với Hvedrungr hủy diệt trong trận chiến cuối cùng.</t>
         </is>
       </c>
@@ -19050,7 +19050,7 @@
       <c r="M286" t="inlineStr">
         <is>
           <t>Những ứng viên được tuyển chọn từ khắp Solaris, có khả năng kết nối ý thức với cỗ máy chiến đấu khổng lồ Exostrider thông qua giao diện cơ học bên ngoài.
-Những Đồng Bộ Giả này có thể điều khiển Exostrider ở một mức độ nhất định nhờ Resonance Tăng Cường. Để tìm kiếm và đào tạo những phi công hiếm có này, Startorch Academy đã thành lập Rabelle College.</t>
+Những Đồng Bộ Giả này có thể điều khiển Exostrider ở một mức độ nhất định nhờ Cộng Hưởng Tăng Cường. Để tìm kiếm và đào tạo những phi công hiếm có này, Học viện Startorch đã thành lập Rabelle College.</t>
         </is>
       </c>
     </row>
@@ -19384,8 +19384,8 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Cơ sở hạ tầng bảo vệ chuyên dụng do Startorch Academy phát triển, sử dụng vật liệu đảo ngược kỹ thuật từ sợi và lớp phủ bề mặt của Exostrider. Nó cung cấp khả năng kháng lại sự ô nhiễm của Vật Chất Hư Không ở một mức độ nhất định.
-Hiện đã được triển khai như biện pháp bảo vệ tiêu chuẩn tại các trại của Spacetrek Collective, tiền đồn nghiên cứu và trung tâm trung chuyển. Công trình lớn nhất là Mái Vòm Kháng Hư Không bao quanh Startorch Academy.</t>
+          <t>Cơ sở hạ tầng bảo vệ chuyên dụng do Học viện Startorch phát triển, sử dụng vật liệu đảo ngược kỹ thuật từ sợi và lớp phủ bề mặt của Exostrider. Nó cung cấp khả năng kháng lại sự ô nhiễm của Vật Chất Hư Không ở một mức độ nhất định.
+Hiện đã được triển khai như biện pháp bảo vệ tiêu chuẩn tại các trại của Spacetrek Collective, tiền đồn nghiên cứu và trung tâm trung chuyển. Công trình lớn nhất là Mái Vòm Kháng Hư Không bao quanh Học viện Startorch.</t>
         </is>
       </c>
     </row>
@@ -19451,7 +19451,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Cư dân bản địa của Lahai-Roi. Họ đã sinh sống trong hang động ngầm từ rất lâu trước khi Spacetrek Collective đến. Giờ đây, họ duy trì mối quan hệ hợp tác với tập đoàn này.
+          <t>Cư dân bản địa của Lahai-Roi. Họ đã sinh sống trong hang động ngầm từ rất lâu trước khi Tập Đoàn Spacetrek đến. Giờ đây, họ duy trì mối quan hệ hợp tác với tập đoàn này.
 Qua việc quan sát chu kỳ hoạt động của Reactor Drive, người Roya đã tạo ra lịch riêng cho mình. Họ hướng dẫn sự phát triển và di cư của Exoswarm, một nhiệm vụ thiêng liêng mà họ coi là sứ mệnh của bộ tộc.</t>
         </is>
       </c>
@@ -19518,7 +19518,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Dự án kéo dài hàng thập kỷ của Spacetrek Collective nhằm thay thế Bộ Phản Ứng trên bầu trời bằng Helios – một mặt trời nhân tạo do Viện Nghiên Cứu chế tạo.
+          <t>Dự án kéo dài hàng thập kỷ của Spacetrek Collective nhằm thay thế Bộ Phản Ứng trên bầu trời bằng Helios – một mặt trời nhân tạo do Viện Nghiên cứu chế tạo.
 Mục tiêu cuối cùng là thu hồi Bộ Phản Ứng làm nguồn năng lượng đánh thức Exostrider đang say giấc trong vùng băng giá, đồng thời duy trì hệ sinh thái ổn định của Lahai-Roi.</t>
         </is>
       </c>
@@ -19585,7 +19585,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Mặt trời nhân tạo do Viện Nghiên Cứu Spacetrek Collective chế tạo để thay thế Bộ Truyền động Phản ứng trong Lễ Mặt trời New.
+          <t>Mặt trời nhân tạo do Viện Nghiên cứu Spacetrek Collective chế tạo để thay thế Bộ Truyền động Phản ứng trong Lễ Mặt trời Mới.
 Để vận hành thành công, nó cần dữ liệu môi trường từ Hyvatia và dữ liệu quan sát thô về Bộ Truyền động Phản ứng do Heliogyre cung cấp.</t>
         </is>
       </c>
@@ -19652,8 +19652,8 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Vùng đất linh thiêng của Roya và nơi ở của Lục Heliodic. Nơi này bảo vệ các bộ phận Exostrider và đóng vai trò là kho lưu trữ trung tâm cho tất cả hồ sơ của Roya.
-Với mỗi chu kỳ hoạt động của Reactor Drive, Solisylum sẽ tính toán độ ổn định, theo dõi sự ra đời và phát triển của Exoswarm, đồng thời giám sát sự trở lại của chúng với Exostrider.</t>
+          <t>Đất thiêng của Roya và nơi ngự trị của Lục Heliodic. Nơi đây bảo vệ các bộ phận Exostrider và lưu trữ kho lưu trữ trung tâm của tất cả hồ sơ Royan.
+Với mỗi chu kỳ hoạt động của Reactor Drive, Solisylum sẽ tính toán độ ổn định, theo dõi sự ra đời và phát triển của Exoswarm, cũng như giám sát sự trở về của chúng với Exostrider.</t>
         </is>
       </c>
     </row>
@@ -19720,7 +19720,7 @@
       <c r="M296" t="inlineStr">
         <is>
           <t>Một tạo tác chỉ được Lục Heliodic sử dụng để quan sát Bộ Điều Khiển Phản Ứng.
-Trong New Solar Ceremony, nó cung cấp cho Helios dữ liệu quan sát thô về Bộ Điều Khiển Phản Ứng.</t>
+Trong Lễ Hội Mặt Trời Mới, nó cung cấp cho Helios dữ liệu quan sát thô về Bộ Điều Khiển Phản Ứng.</t>
         </is>
       </c>
     </row>
@@ -20504,7 +20504,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Được biết đến với tên gọi chính thức là Tập đoàn Spacetrek: Startorch Academy, thành phố học thuật không biên giới này đào tạo các Đồng Bộ Giả và dẫn đầu nghiên cứu về cỗ máy khổng lồ mang tên Exostrider. Cái tên của nó thể hiện tinh thần cốt lõi: "giữ ngọn lửa tìm tòi và thắp sáng ngọn đuốc văn minh". Tại đây, những người tìm kiếm tri thức từ khắp nơi trên thế giới tụ hội, tri thức được trao đổi tự do, và các nền văn hóa giao thoa hòa quyện.</t>
+          <t>Được biết đến với tên gọi chính thức là Tập đoàn Spacetrek: Học viện Startorch, thành phố học thuật không biên giới này đào tạo các Đồng Bộ Giả và dẫn đầu nghiên cứu về cỗ máy khổng lồ mang tên Exostrider. Cái tên của nó thể hiện tinh thần cốt lõi: "giữ ngọn lửa tìm tòi và thắp sáng ngọn đuốc văn minh". Tại đây, những người tìm kiếm tri thức từ khắp nơi trên thế giới tụ hội, tri thức được trao đổi tự do, và các nền văn hóa giao thoa hòa quyện.</t>
         </is>
       </c>
     </row>
@@ -20638,7 +20638,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Một loại Discord sinh ra từ Hắc Triều.</t>
+          <t>Một loại Tacet Discord sinh ra từ Hắc Triều.</t>
         </is>
       </c>
     </row>
@@ -20768,7 +20768,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Nằm ở ngoại ô thành phố Septimont, đây là "trạm không vận" nơi các Chiến Binh vượt qua hẻm núi để đến và rời Sanguis Plateaus.</t>
+          <t>Nằm ở ngoại ô thành phố Septimont, đây là "trạm không vận" nơi các Chiến Binh vượt qua hẻm núi để đến và rời Cao Nguyên Sanguis.</t>
         </is>
       </c>
     </row>
@@ -20963,7 +20963,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Một Echo hình chiếc tù và lớn. Tiếng rít the thé và kéo dài của Hornett được dùng để báo hiệu bắt đầu hoặc kết thúc các cuộc săn lớn.</t>
+          <t>Một Tiếng Vọng hình chiếc tù và lớn. Tiếng rít the thé và kéo dài của Hornett được dùng để báo hiệu bắt đầu hoặc kết thúc các cuộc săn lớn.</t>
         </is>
       </c>
     </row>
@@ -21096,8 +21096,8 @@
       <c r="M317" t="inlineStr">
         <is>
           <t>Một loại lửa độc đáo, tạo ra bằng cách đốt các khoáng chất đặc biệt. Ngoại hình của nó giống ánh mặt trời hơn là lửa thông thường. Loại và tỷ lệ khoáng chất chính xác để tạo ra ngọn lửa này là bí mật được truyền lại qua các thế hệ Nữ Tư Tế.
-Dù Ngọn Sacred Flame không mang sức mạnh đặc biệt, các Nữ Tư Tế vẫn dẫn truyền năng lượng Resonance qua nó, dùng ánh sáng để nhìn thấy tương lai và đưa ra lời tiên tri.
-Nhưng với các Nữ Tư Tế, Ngọn Sacred Flame không chỉ là phương tiện bói toán. Họ coi đó là "ánh sáng thiên giới giáng trần", thường gọi là "ngọn lửa".</t>
+Dù Ngọn Lửa Thiêng không mang sức mạnh đặc biệt, các Nữ Tư Tế vẫn dẫn truyền năng lượng Cộng Hưởng qua nó, dùng ánh sáng để nhìn thấy tương lai và đưa ra lời tiên tri.
+Nhưng với các Nữ Tư Tế, Ngọn Lửa Thiêng không chỉ là phương tiện bói toán. Họ coi đó là "ánh sáng thiên giới giáng trần", thường gọi là "ngọn lửa".</t>
         </is>
       </c>
     </row>
@@ -21297,8 +21297,8 @@
       <c r="M320" t="inlineStr">
         <is>
           <t>Griffrex vốn xuất thân từ vùng Septimont, từng chung sống hòa bình với tổ tiên của người Septimont khi họ tìm nơi trú ẩn tại Rinascita.
-Nhưng cơn Thủy triều Đen đầu tiên đã tàn phá Dãy núi Biên giới – môi trường sống của Griffrex – đẩy loài này đến bờ vực tuyệt chủng. Từ đó, Griffrex chủ yếu tồn tại dưới dạng Tiếng vọng Chung, được tạo ra ở tần số cố định từ Đèn hiệu Cộng hưởng.
-Theo thời gian, người Septimont nhận ra những tiếng vọng này vẫn giữ bản năng săn mồi và khả năng cảm nhận các tần số khác. Vì vậy, họ huấn luyện chúng thành Common Echoes phục vụ mục đích săn bắn, truy lùng và tấn công các sinh vật của Dark Tide.</t>
+Nhưng cơn Thủy triều Đen đầu tiên đã tàn phá Dãy núi Biên giới – môi trường sống của Griffrex – đẩy loài này đến bờ vực tuyệt chủng. Từ đó, Griffrex chủ yếu tồn tại dưới dạng Echo Chung, được tạo ra ở tần số cố định từ Đèn hiệu Cộng hưởng.
+Theo thời gian, người Septimont nhận ra những Echo này vẫn giữ bản năng săn mồi và khả năng cảm nhận các tần số khác. Vì vậy, họ huấn luyện chúng thành Common Echoes phục vụ mục đích săn bắn, truy lùng và tấn công các sinh vật của Dark Tide.</t>
         </is>
       </c>
     </row>
@@ -21497,7 +21497,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Một Echo ẩn sâu trong rừng Maroonwood. Nằm ở độ cao gần bằng Earthrend Wedge và thuộc tầng giữa thấp của cao nguyên Sanguis, đây là chiến trường chính nơi các Gladiator giao tranh ác liệt với Dark Tide và những sinh vật của nó.</t>
+          <t>Một Tổ Tacet ẩn sâu trong rừng Maroonwood. Nằm ở độ cao gần bằng Earthrend Wedge và thuộc tầng giữa thấp của cao nguyên Sanguis, đây là chiến trường chính nơi các Chiến Binh Gladiator giao tranh ác liệt với Dark Tide và những sinh vật của nó.</t>
         </is>
       </c>
     </row>
@@ -21562,7 +21562,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Một thị trấn Gladiator bị lãng quên nằm ở Vùng Đất Hoang, thuộc tầng thấp của Sanguis Plateaus.</t>
+          <t>Một thị trấn Gladiator bị lãng quên nằm ở Vùng Đất Hoang, thuộc tầng thấp của Cao Nguyên Sanguis.</t>
         </is>
       </c>
     </row>
@@ -21757,7 +21757,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Những nạn nhân bị Echo tha hóa trong "Thủy Triều Hắc Ám", mất hết nhận thức về bản thân. Thân thể họ thường hóa thành những bức tượng đá, giữ nguyên kích thước ban đầu. Những cá nhân này không ngừng thì thầm và lẩm nhẩm những lời vô nghĩa cùng "bài thánh ca ca tụng Thủy Triều Hắc Ám". Âm thanh từ Hollow Figures đã được xác nhận có khả năng gây suy nhược tinh thần, ảnh hưởng đến nhận thức và sự ổn định tâm lý của người bình thường ở một mức độ nhất định.</t>
+          <t>Những nạn nhân bị Tổ Tacet tha hóa trong "Thủy Triều Hắc Ám", mất hết nhận thức về bản thân. Thân thể họ thường hóa thành những bức tượng đá, giữ nguyên kích thước ban đầu. Những cá nhân này không ngừng thì thầm và lẩm nhẩm những lời vô nghĩa cùng "bài thánh ca ca tụng Thủy Triều Hắc Ám". Âm thanh từ Hollow Figures đã được xác nhận có khả năng gây suy nhược tinh thần, ảnh hưởng đến nhận thức và sự ổn định tâm lý của người bình thường ở một mức độ nhất định.</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Loại này bao gồm Hologram Echo: Chest Mimic, Hologram Echo: Junrock, Hologram Echo: Drake, Hologram Echo: Hoartoise và Hologram Echo: Puff.</t>
+          <t>Loại này bao gồm Hologram Echo: Chest Mimic, Hologram Echo: Junrock, Hologram Echo: Drake, Hologram Echo: Hoartoise, and Hologram Echo: Puff.</t>
         </is>
       </c>
     </row>
@@ -21952,7 +21952,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Loại này bao gồm Tacetite Spikes với Optional Mô-đun II, Glacio Beacon, Hologram Echo: Junrock với Optional Mô-đun I, Frost Spout, Hologram Echo: Puff và Freeze Jet.</t>
+          <t>Loại này bao gồm Tacetite Spikes với Optional Module II, Glacio Beacon, Hologram Echo: Junrock với Optional Module I, Frost Spout, Hologram Echo: Puff và Freeze Jet.</t>
         </is>
       </c>
     </row>
@@ -22017,7 +22017,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Loại này bao gồm: Tacetite Barrage với Optional Mô-đun I, Hologram Echo: Drake, Hologram Echo: Hoartoise với Optional Mô-đun II, Hologram Echo: Chest Mimic và Burst Launcher.</t>
+          <t>Loại này bao gồm: Tacetite Barrage với Optional Module I, Hologram Echo: Drake, Hologram Echo: Hoartoise với Optional Module II, Hologram Echo: Chest Mimic và Burst Launcher.</t>
         </is>
       </c>
     </row>
@@ -22147,7 +22147,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Loại này bao gồm Stun Emitter, Tacetite Spikes với Optional Mô-đun I, Thunder Lance và Shock Inductor.</t>
+          <t>Loại này bao gồm Stun Emitter, Tacetite Spikes với Optional Module I, Thunder Lance và Shock Inductor.</t>
         </is>
       </c>
     </row>
@@ -22212,7 +22212,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Nimbus Wraith và Tacet Discord bị Hologram Echo đánh bại: Kẻ bắt chước Rương có thể rơi vật phẩm này.</t>
+          <t>Hồn Ma Nimbus và Tacet Discord bị Hologram Echo đánh bại: Kẻ bắt chước Rương có thể rơi vật phẩm này.</t>
         </is>
       </c>
     </row>
@@ -22277,7 +22277,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>KU-Money's Shop sẽ xuất hiện sau một số đợt sóng nhất định, nơi cậu có thể dùng Sim Credits để mua Chiến thuật và vật phẩm.</t>
+          <t>Cửa hàng KU-Money sẽ xuất hiện sau một số đợt sóng nhất định, nơi cậu có thể dùng Sim Credit để mua Chiến thuật và vật phẩm.</t>
         </is>
       </c>
     </row>
@@ -22342,7 +22342,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Tactic Set tạo ra Chuỗi Sét nảy giữa các mục tiêu, kích hoạt khi gây hiệu ứng Tê Liệt lên đối phương.</t>
+          <t>Bộ Chiến Thuật tạo ra Chuỗi Sét nảy giữa các mục tiêu, kích hoạt khi gây hiệu ứng Tê Liệt lên đối phương.</t>
         </is>
       </c>
     </row>
@@ -22407,7 +22407,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Tactic Set tối ưu hóa hiệu suất thu thập tài nguyên và chuyển hóa lượng tài nguyên dư thừa thành sức mạnh tấn công.</t>
+          <t>Bộ Chiến Thuật tối ưu hóa hiệu suất thu thập tài nguyên và chuyển hóa lượng tài nguyên dư thừa thành sức mạnh tấn công.</t>
         </is>
       </c>
     </row>
@@ -22472,7 +22472,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Tactic Set tập trung vào kiểm soát hỏa lực bằng cách tăng Attack Speed và hiệu ứng Control.</t>
+          <t>Bộ Chiến Thuật tập trung vào kiểm soát hỏa lực bằng cách tăng Tốc Độ Tấn Công và hiệu ứng Điều Khiển.</t>
         </is>
       </c>
     </row>
@@ -22537,7 +22537,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Chiến thuật cốt lõi được khuyến nghị cao nhất của một Tactic Set.</t>
+          <t>Chiến thuật cốt lõi được khuyến nghị cao nhất của một Bộ Chiến Thuật.</t>
         </is>
       </c>
     </row>
@@ -22602,7 +22602,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Loại chiến thuật này gia tăng Tấn Công, Crit. Rate và Sát Thương của một số Thuộc Tính, đồng thời giảm Kháng của Tacet Discord, nâng cao hiệu quả tấn công.</t>
+          <t>Loại chiến thuật này gia tăng ATK, Crit. Rate và Sát Thương của một số Thuộc Tính, đồng thời giảm Kháng của Tacet Discord, nâng cao hiệu quả tấn công.</t>
         </is>
       </c>
     </row>
@@ -22667,7 +22667,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Loại chiến thuật này tăng cường sức mạnh cho các Combat Machines trong phạm vi nhất định khi kích hoạt.</t>
+          <t>Loại chiến thuật này tăng cường sức mạnh cho các Máy Chiến Đấu trong phạm vi nhất định khi kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -22992,7 +22992,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Thiết bị chuyên dụng do Spacetrek Collective phát triển để phục vụ nghiên cứu tại Roya Frostlands. Nó buộc các thực thể có mức Voidmatter dao động trở lại trạng thái quan sát được để sử dụng thực tế. Ở những khu vực có tín hiệu ổn định, thiết bị có thể được triển khai trực tiếp đến vị trí của người dùng.</t>
+          <t>Thiết bị chuyên dụng do Tập Đoàn Spacetrek phát triển để phục vụ nghiên cứu tại Roya Frostlands. Nó buộc các thực thể có mức Voidmatter dao động trở lại trạng thái quan sát được để sử dụng thực tế. Ở những khu vực có tín hiệu ổn định, thiết bị có thể được triển khai trực tiếp đến vị trí của người dùng.</t>
         </is>
       </c>
     </row>
@@ -23057,7 +23057,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Trạm không gian A Court of Savantae được phóng lên quỹ đạo gần Solaris-3 trước khi Etheric Sea hoàn toàn bao phủ hành tinh. Nhiệm vụ chính của nó là nghiên cứu các giọt Ether, nhằm mở đường cho việc khám phá không gian sâu hơn.</t>
+          <t>Trạm không gian A Court of Savantae được phóng lên quỹ đạo gần Solaris-3 trước khi Biển Ether hoàn toàn bao phủ hành tinh. Nhiệm vụ chính của nó là nghiên cứu các giọt Ether, nhằm mở đường cho việc khám phá không gian sâu hơn.</t>
         </is>
       </c>
     </row>
@@ -23317,7 +23317,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Một tập đoàn dược phẩm có trụ sở tại Liên bang New. Công nghệ cốt lõi của họ bắt nguồn từ việc phát triển Ichor - một bước đột phá y học bị bao phủ bởi những tranh cãi không ngừng.</t>
+          <t>Một tập đoàn dược phẩm có trụ sở tại Liên bang Mới. Công nghệ cốt lõi của họ bắt nguồn từ việc phát triển Ichor - một bước đột phá y học bị bao phủ bởi những tranh cãi không ngừng.</t>
         </is>
       </c>
     </row>
@@ -23447,7 +23447,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Chiếc bánh lớn dành tặng kỷ niệm 1 năm ra mắt phiên bản Beta của Second Coming of Solaris, đồng thời là trung tâm điều khiển cho trình mô phỏng của nó. Khi được hỏi về thiết kế hình bánh của trung tâm, trưởng nhóm thiết kế Encore trả lời: "Sinh nhật mà không có bánh thì còn gì vui nữa! Chúc mừng kỷ niệm!"</t>
+          <t>Chiếc bánh lớn dành tặng kỷ niệm 1 năm ra mắt phiên bản Beta của Sự Trở Lại Của Solaris, đồng thời là trung tâm điều khiển cho trình mô phỏng của nó. Khi được hỏi về thiết kế hình bánh của trung tâm, trưởng nhóm thiết kế Encore trả lời: "Sinh nhật mà không có bánh thì còn gì vui nữa! Chúc mừng kỷ niệm!"</t>
         </is>
       </c>
     </row>
@@ -23577,7 +23577,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Được biết đến với tên gọi chính thức là "Khối Dư Âm", đây là những trí tuệ nhân tạo tiên tiến được tạo ra cho Second Coming of Solaris, sử dụng khả năng của Encore và sự hỗ trợ vi xử lý từ Tethys. Lưu ý: Khối Dư Âm là các mô phỏng thử nghiệm, được hệ thống tự động tạo ra. Tính cách và hành động của chúng trong trò chơi không phản ánh những cá nhân có thật.</t>
+          <t>Được biết đến với tên gọi chính thức là "Khối Dư Âm", đây là những trí tuệ nhân tạo tiên tiến được tạo ra cho Sự Trở Lại Của Solaris, sử dụng khả năng của Encore và sự hỗ trợ vi xử lý từ Tethys. Lưu ý: Khối Dư Âm là các mô phỏng thử nghiệm, được hệ thống tự động tạo ra. Tính cách và hành động của chúng trong trò chơi không phản ánh những cá nhân có thật.</t>
         </is>
       </c>
     </row>
@@ -23707,7 +23707,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Sonoro Sphere là không gian chứa mật độ Năng Lượng Tàn Dư dày đặc, có khả năng lưu giữ thông tin xuyên chiều. Trong văn hóa Huanglong, những cõi vô hình như vậy—không thực cũng chẳng hư—thường được gọi là "ảo ảnh".</t>
+          <t>Khối Sonoro là không gian chứa mật độ Năng Lượng Tàn Dư dày đặc, có khả năng lưu giữ thông tin xuyên chiều. Trong văn hóa Huanglong, những cõi vô hình như vậy—không thực cũng chẳng hư—thường được gọi là "ảo ảnh".</t>
         </is>
       </c>
     </row>
@@ -23772,7 +23772,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Một đường truyền tín hiệu. Trong quá trình mô phỏng, Second Coming of Solaris đã tạm thời kết nối với Tethys Hệ thống, tạo ra kênh liên lạc tạm thời giữa chúng.</t>
+          <t>Một đường truyền tín hiệu. Trong quá trình mô phỏng, Sự Trở Lại Của Solaris đã tạm thời kết nối với Hệ Thống Tethys, tạo ra kênh liên lạc tạm thời giữa chúng.</t>
         </is>
       </c>
     </row>
@@ -23837,7 +23837,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Một nhóm lính đánh thuê của New Federation do Calcharo lãnh đạo.</t>
+          <t>Một nhóm lính đánh thuê của Liên Bang Mới do Calcharo lãnh đạo.</t>
         </is>
       </c>
     </row>
@@ -24032,7 +24032,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Chòm sao sáng nhất đêm thu, ẩn chứa vô vàn truyền thuyết. Một thi nhân của Golden Anthem từng viết: *"Ta là chim ưng đêm với đôi cánh rực lửa, bay về phía Celestial Steed, ngợi ca và chiêm ngưỡng chân dung của nó."* Hình ảnh ấy luôn gợi nhớ đến Sentinel của Rinascita. Nhưng tại sao lại bay về phía nó và chiêm ngưỡng chân dung? Có lẽ bài thơ muốn truyền tải một thông điệp nào đó.</t>
+          <t>Chòm sao sáng nhất đêm thu, ẩn chứa vô vàn truyền thuyết. Một thi nhân của Golden Anthem từng viết: *"Ta là chim ưng đêm với đôi cánh rực lửa, bay về phía Thiên Mã, ngợi ca và chiêm ngưỡng chân dung của nó."* Hình ảnh ấy luôn gợi nhớ đến Sentinel của Rinascita. Nhưng tại sao lại bay về phía nó và chiêm ngưỡng chân dung? Có lẽ bài thơ muốn truyền tải một thông điệp nào đó.</t>
         </is>
       </c>
     </row>
@@ -24097,7 +24097,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Music được cấu thành từ tần số, cũng như mọi thứ khác. Vì vậy, mọi thứ đều ngân vang giai điệu riêng của mình. Khả năng Forte của Ciaccona cho phép cô cảm nhận những giai điệu ấy; bằng cách điều chỉnh chúng, cô tạo ra một Sonoro Sphere trong tay, nơi những câu chuyện và ký ức được mang theo trong âm nhạc tái hiện lại. Hiểu biết càng sâu về giai điệu, những câu chuyện cô có thể triệu hồi càng phong phú.</t>
+          <t>Âm nhạc được cấu thành từ tần số, cũng như mọi thứ khác. Vì vậy, mọi thứ đều ngân vang giai điệu riêng của mình. Khả năng Forte của Ciaccona cho phép cô cảm nhận những giai điệu ấy; bằng cách điều chỉnh chúng, cô tạo ra một Sonoro Sphere trong tay, nơi những câu chuyện và ký ức được mang theo trong âm nhạc tái hiện lại. Hiểu biết càng sâu về giai điệu, những câu chuyện cô có thể triệu hồi càng phong phú.</t>
         </is>
       </c>
     </row>
@@ -24162,7 +24162,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Gây Glacio DMG lên kẻ địch quanh điểm va chạm.</t>
+          <t>Gây Sát Thương Glacio lên kẻ địch quanh điểm va chạm.</t>
         </is>
       </c>
     </row>
@@ -24227,7 +24227,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Gây Aero DMG dọc theo quỹ đạo di chuyển.</t>
+          <t>Gây Sát Thương Aero dọc theo quỹ đạo di chuyển.</t>
         </is>
       </c>
     </row>
@@ -24292,7 +24292,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Attack cận chiến kẻ địch để gây sát thương. Không được hưởng lợi từ các hiệu ứng tăng Attack Speed.</t>
+          <t>Tấn công cận chiến kẻ địch để gây DMG. Không được hưởng lợi từ các hiệu ứng tăng Tốc Độ Tấn Công.</t>
         </is>
       </c>
     </row>
@@ -24422,7 +24422,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Tăng mạnh tầm xa và hệ số sát thương.</t>
+          <t>Tăng mạnh tầm xa và hệ số DMG.</t>
         </is>
       </c>
     </row>
@@ -24491,11 +24491,11 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Gây Aero DMG lên kẻ địch xung quanh bằng 100% Tấn Công của Rover. Sau đó, tăng Movement Speed lên 48%, giảm dần về 0% trong 4 giây. Mỗi 1% Movement Speed tăng thêm trong thời gian này sẽ cộng thêm 0.8% Sát Thương.
-&lt;color=Highlight&gt;At Resonator Lv. 5&lt;/color&gt;
-Tăng Movement Speed lên 64%, tỷ lệ chuyển đổi sát thương tăng lên 1%.
-&lt;color=Highlight&gt;At Resonator Lv. 10&lt;/color&gt;
-Tăng Movement Speed lên 80%, tỷ lệ chuyển đổi sát thương tăng lên 1.2%.</t>
+          <t>Gây Sát Thương Aero lên kẻ địch xung quanh bằng 100% ATK của Rover. Sau đó, tăng Tốc Độ Di Chuyển lên 48%, giảm dần về 0% trong 4 giây. Mỗi 1% Tốc Độ Di Chuyển tăng thêm trong thời gian này sẽ cộng thêm 0.8% Sát Thương.
+&lt;color=Highlight&gt;Ở Cấp Độ Resonator 5&lt;/color&gt;
+Tăng Tốc Độ Di Chuyển lên 64%, tỷ lệ chuyển đổi DMG tăng lên 1%.
+&lt;color=Highlight&gt;Ở Cấp Độ Resonator 10&lt;/color&gt;
+Tăng Tốc Độ Di Chuyển lên 80%, tỷ lệ chuyển đổi DMG tăng lên 1.2%.</t>
         </is>
       </c>
     </row>
@@ -24564,11 +24564,11 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Gây Fusion DMG lên kẻ địch xung quanh bằng 100% Attack của Galbrena. Sau đó, tăng Attack Speed lên 30% trong 5 giây. Mỗi lần gây sát thương trong thời gian này sẽ tăng Crit. Rate của Vũ Khí lên 1% trong 5 giây, tối đa 20 lần.
-&lt;color=Highlight&gt;At Resonator Lv. 5&lt;/color&gt;
-Tăng Attack Speed lên 40%, Crit. Rate giờ có thể chồng chất lên 30 lần.
-&lt;color=Highlight&gt;At Resonator Lv. 10&lt;/color&gt;
-Tăng Attack Speed lên 50%, Crit. Rate giờ có thể chồng chất lên 40 lần.</t>
+          <t>Gây Sát Thương Fusion lên kẻ địch xung quanh bằng 100% ATK của Galbrena. Sau đó, tăng Tốc Độ ATK lên 30% trong 5 giây. Mỗi lần gây DMG trong thời gian này sẽ tăng Crit. Rate của Vũ Khí lên 1% trong 5 giây, tối đa 20 lần.
+&lt;color=Highlight&gt;Ở Cấp Độ Resonator 5&lt;/color&gt;
+Tăng Tốc Độ ATK lên 40%, Crit. Rate giờ có thể chồng chất lên 30 lần.
+&lt;color=Highlight&gt;Ở Cấp Độ Resonator 10&lt;/color&gt;
+Tăng Tốc Độ ATK lên 50%, Crit. Rate giờ có thể chồng chất lên 40 lần.</t>
         </is>
       </c>
     </row>
@@ -24637,11 +24637,11 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Gây Aero DMG lên kẻ địch xung quanh bằng 40% HP tối đa của Iuno. Sau đó, mất 30% HP hiện tại để tăng Tấn Công lên 40% HP tối đa trong 4 giây. Đánh trúng kẻ địch trong thời gian này sẽ hồi 1.5% HP tối đa.
-&lt;color=Highlight&gt;At Resonator Lv. 5&lt;/color&gt;
-Tỷ lệ chuyển đổi Tấn Công tăng lên 60%, thời gian kéo dài lên 5 giây.
-&lt;color=Highlight&gt;At Resonator Lv. 10&lt;/color&gt;
-Tỷ lệ chuyển đổi Tấn Công tăng lên 80%, thời gian kéo dài lên 6 giây.</t>
+          <t>Gây Sát Thương Aero lên kẻ địch xung quanh bằng 40% HP tối đa của Iuno. Sau đó, mất 30% HP hiện tại để tăng ATK lên 40% HP tối đa trong 4 giây. Đánh trúng kẻ địch trong thời gian này sẽ hồi 1.5% HP tối đa.
+&lt;color=Highlight&gt;Ở Cấp Độ Resonator 5&lt;/color&gt;
+Tỷ lệ chuyển đổi ATK tăng lên 60%, thời gian kéo dài lên 5 giây.
+&lt;color=Highlight&gt;Ở Cấp Độ Resonator 10&lt;/color&gt;
+Tỷ lệ chuyển đổi ATK tăng lên 80%, thời gian kéo dài lên 6 giây.</t>
         </is>
       </c>
     </row>
@@ -24710,11 +24710,11 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Summon một Nốt Hài Hòa gây Aero DMG lên kẻ địch xung quanh bằng 10% Tấn Công của Ciaccona mỗi 0.5 giây trong 10 giây. Kẻ địch bị tấn công bởi kỹ năng này sẽ chịu Sát Thương tăng thêm 3% và Movement Speed giảm 1% trong 5 giây, tối đa chồng chất 20 lần.
-&lt;color=Highlight&gt;At Resonator Lv. 5&lt;/color&gt;
-Sát Thương kẻ địch phải chịu tăng thêm 4%, Movement Speed giảm 2%.
-&lt;color=Highlight&gt;At Resonator Lv. 10&lt;/color&gt;
-Sát Thương kẻ địch phải chịu tăng thêm 5%, Movement Speed giảm 3%.</t>
+          <t>Triệu hồi một Nốt Hài Hòa gây Sát Thương Aero lên kẻ địch xung quanh bằng 10% ATK của Ciaccona mỗi 0.5 giây trong 10 giây. Kẻ địch bị tấn công bởi kỹ năng này sẽ chịu Sát Thương tăng thêm 3% và Tốc Độ Di Chuyển giảm 1% trong 5 giây, tối đa chồng chất 20 lần.
+&lt;color=Highlight&gt;Khi Resonator đạt cấp 5&lt;/color&gt;
+Sát Thương kẻ địch phải chịu tăng thêm 4%, Tốc Độ Di Chuyển giảm 2%.
+&lt;color=Highlight&gt;Khi Resonator đạt cấp 10&lt;/color&gt;
+Sát Thương kẻ địch phải chịu tăng thêm 5%, Tốc Độ Di Chuyển giảm 3%.</t>
         </is>
       </c>
     </row>
@@ -24779,7 +24779,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Phóng ngẫu nhiên một ngôi sao rơi xuống kẻ địch, gây Fusion DMG.</t>
+          <t>Phóng ngẫu nhiên một ngôi sao rơi xuống kẻ địch, gây Sát Thương Fusion.</t>
         </is>
       </c>
     </row>
@@ -24844,7 +24844,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Phun liên tục lửa về phía trước, gây Havoc DMG. Không thể hưởng lợi từ hiệu ứng tăng Attack Speed.</t>
+          <t>Phun liên tục lửa về phía trước, gây Sát Thương Havoc. Không thể hưởng lợi từ hiệu ứng tăng Tốc Độ Tấn Công.</t>
         </is>
       </c>
     </row>
@@ -24909,7 +24909,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Một Feilian Beringal được triệu hồi, đứng yên tại chỗ gây Aero DMG cho kẻ địch xung quanh. Không thể hưởng lợi từ các bonus Attack Speed.</t>
+          <t>Một Feilian Beringal được triệu hồi, đứng yên tại chỗ gây Sát Thương Aero cho kẻ địch xung quanh. Không thể hưởng lợi từ các bonus Tốc Độ Tấn Công.</t>
         </is>
       </c>
     </row>
@@ -24974,7 +24974,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Kích hoạt ngẫu nhiên một cái bẫy, phát nổ sau một lúc hoặc khi chạm vào kẻ địch, gây Fusion DMG diện rộng.</t>
+          <t>Kích hoạt ngẫu nhiên một cái bẫy, phát nổ sau một lúc hoặc khi chạm vào kẻ địch, gây Sát Thương Fusion diện rộng.</t>
         </is>
       </c>
     </row>
@@ -25039,7 +25039,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Weapons bắn đạn va chạm đạn đạo, như Isomer Bolt và Blazing Star.</t>
+          <t>Vũ khí bắn đạn va chạm đạn đạo, như Isomer Bolt và Blazing Star.</t>
         </is>
       </c>
     </row>
@@ -25104,7 +25104,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Weapons có thể triệu hồi phản chiếu Echo, như Feilian Shock và Sanguine Wheel.</t>
+          <t>Vũ khí có thể triệu hồi phản chiếu Echo, như Feilian Shock và Sanguine Wheel.</t>
         </is>
       </c>
     </row>
@@ -25169,7 +25169,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Weapons phóng chùm năng lượng, như Zenith Windblade và Glittering Ray.</t>
+          <t>Vũ khí phóng chùm năng lượng, như Zenith Windblade và Glittering Ray.</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Weapons có hiệu ứng đặc biệt, như Rampant Fire và Explosive Omen.</t>
+          <t>Vũ khí có hiệu ứng đặc biệt, như Rampant Fire và Explosive Omen.</t>
         </is>
       </c>
     </row>
@@ -25299,7 +25299,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Một số vũ khí có thể bị hấp thụ để tiến hóa vũ khí khác thành Ultimate Form. Yêu cầu tiến hóa sẽ khác nhau tùy vào từng Vũ Khí. Weapons sau tiến hóa sẽ kế thừa tất cả hiệu ứng tăng cường của vũ khí bị hấp thụ.</t>
+          <t>Một số vũ khí có thể bị hấp thụ để tiến hóa vũ khí khác thành Hình Thái Tối Thượng. Yêu cầu tiến hóa sẽ khác nhau tùy vào từng Vũ Khí. Vũ khí sau tiến hóa sẽ kế thừa tất cả hiệu ứng tăng cường của vũ khí bị hấp thụ.</t>
         </is>
       </c>
     </row>
@@ -25366,7 +25366,7 @@
       <c r="M382" t="inlineStr">
         <is>
           <t>Exostrider tỏa ra ánh sáng và hơi ấm từ Lò Phản Ứng, che chở sự sống khỏi băng giá chết chóc. Biết ơn món quà này, tộc Roya tôn thờ Lò Phản Ứng như mặt trời của họ. Họ tự nguyện thu thập những "tế bào" của Exostrider, biến công việc lặng thầm này thành sứ mệnh của bộ tộc.
-Giờ đây, lời thề cổ xưa đã hoàn thành. Khi mặt trời mới mọc, họ tổ chức Lễ Mặt Trời New, vừa để kỷ niệm sự hồi sinh, vừa để nhắc nhở đồng bào về mục đích đã đưa họ đến con đường này.</t>
+Giờ đây, lời thề cổ xưa đã hoàn thành. Khi mặt trời mới mọc, họ tổ chức Lễ Mặt Trời Mới, vừa để kỷ niệm sự hồi sinh, vừa để nhắc nhở đồng bào về mục đích đã đưa họ đến con đường này.</t>
         </is>
       </c>
     </row>
@@ -25561,7 +25561,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Hằng năm, Startorch Academy đều tổ chức một cuộc săn kho báu do một chủ nhân bí ẩn đứng ra. Người tham gia sẽ nhận về vô số phần thưởng, còn người thắng lớn nhất sẽ được ban một điều ước duy nhất. Dù những điều ước ấy luôn được thực hiện theo cách kỳ lạ đến khó hiểu, chính sự lập dị đó lại càng khơi dậy tinh thần cạnh tranh của các học viên, khi họ ra sức vượt qua kẻ chủ mưu vô hình.</t>
+          <t>Hằng năm, Học viện Startorch đều tổ chức một cuộc săn kho báu do một chủ nhân bí ẩn đứng ra. Người tham gia sẽ nhận về vô số phần thưởng, còn người thắng lớn nhất sẽ được ban một điều ước duy nhất. Dù những điều ước ấy luôn được thực hiện theo cách kỳ lạ đến khó hiểu, chính sự lập dị đó lại càng khơi dậy tinh thần cạnh tranh của các học viên, khi họ ra sức vượt qua kẻ chủ mưu vô hình.</t>
         </is>
       </c>
     </row>
@@ -25697,12 +25697,12 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Khi ở trạng thái &lt;color=Highlight&gt;Incarnation&lt;/color&gt;:
-- Đòn &lt;color=Highlight&gt;"Incarnation - Basic Attack"&lt;/color&gt; sẽ khả dụng. Thực hiện tối đa 4 đòn liên tiếp, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; được tính là Sát Thương Resonance Skill. Chu kỳ Basic Attack sẽ không bị reset. Có thể sử dụng trên không.
-- Resonance Skill thay thế &lt;color=Highlight&gt;"Crescent Divinity"&lt;/color&gt; sẽ khả dụng. Gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;. Có thể sử dụng trên không.
-- Đòn &lt;color=Highlight&gt;"Incarnation - Heavy Attack"&lt;/color&gt; sẽ khả dụng. Tấn công mục tiêu trên không với chi phí Stamina, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-- Skill &lt;color=Highlight&gt;"Incarnation - Dodge"&lt;/color&gt; khả dụng khi ở trên không. Có thể sử dụng nhiều lần với chi phí Stamina.
-- Skill &lt;color=Highlight&gt;"Incarnation - Dodge Counter"&lt;/color&gt; sẽ khả dụng. Gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
+          <t>Khi ở trạng thái &lt;color=Highlight&gt;Hóa Thân&lt;/color&gt;:
+- Đòn &lt;color=Highlight&gt;Basic Attack Thay Thế "Hóa Thân - Basic Attack"&lt;/color&gt; sẽ khả dụng. Thực hiện tối đa 4 đòn liên tiếp, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; được tính là Sát Thương Resonance Skill. Chu kỳ Basic Attack sẽ không bị reset. Có thể sử dụng trên không.
+- Kỹ năng Cộng Hưởng thay thế &lt;color=Highlight&gt;"Crescent Divinity"&lt;/color&gt; sẽ khả dụng. Gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;. Có thể sử dụng trên không.
+- Đòn &lt;color=Highlight&gt;Heavy Attack Thay Thế "Hóa Thân - Heavy Attack"&lt;/color&gt; sẽ khả dụng. Tấn công mục tiêu trên không với chi phí Thể Lực, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.
+- Kỹ năng &lt;color=Highlight&gt;Né Tránh Thay Thế "Hóa Thân - Né Tránh"&lt;/color&gt; khả dụng khi ở trên không. Có thể sử dụng nhiều lần với chi phí Thể Lực.
+- Kỹ năng &lt;color=Highlight&gt;Dodge Counter Tránh Thay Thế "Hóa Thân - Dodge Counter Tránh"&lt;/color&gt; sẽ khả dụng. Gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.
 Có thể sử dụng trên không.</t>
         </is>
       </c>
@@ -25772,9 +25772,9 @@
       <c r="M388" t="inlineStr">
         <is>
           <t>Jinhsi có thể chứa tối đa 50 Điểm Tỏa Sáng.
-Khi Jinhsi có mặt trong đội, tất cả Resonators gần đó sẽ nhận được &lt;color=Highlight&gt;Eras in Unity&lt;/color&gt;.
-&lt;color=Highlight&gt;Eras in Unity&lt;/color&gt; mang lại 2 hiệu ứng độc lập:
-Jinhsi nhận 1 Điểm Tỏa Sáng mỗi khi Resonators trong đội gây Sát Thương Thuộc Tính. Hiệu ứng này có thể kích hoạt tối đa 1 lần mỗi 3 giây cho cùng một loại Sát Thương Thuộc Tính. Ngoài ra, Jinhsi nhận 2 Điểm Tỏa Sáng khi Resonators trong đội gây sát thương bằng Đòn Phối Hợp. Hiệu ứng này có thể kích hoạt tối đa 1 lần mỗi 3 giây cho Đòn Phối Hợp cùng Thuộc Tính.</t>
+Khi Jinhsi có mặt trong đội, tất cả Resonator gần đó sẽ nhận được &lt;color=Highlight&gt;Kỷ Nguyên Đồng Tâm&lt;/color&gt;.
+&lt;color=Highlight&gt;Kỷ Nguyên Đồng Tâm&lt;/color&gt; mang lại 2 hiệu ứng độc lập:
+Jinhsi nhận 1 Điểm Tỏa Sáng mỗi khi Resonator trong đội gây Sát Thương Thuộc Tính. Hiệu ứng này có thể kích hoạt tối đa 1 lần mỗi 3 giây cho cùng một loại Sát Thương Thuộc Tính. Ngoài ra, Jinhsi nhận 2 Điểm Tỏa Sáng khi Resonator trong đội gây DMG bằng Đòn Phối Hợp. Hiệu ứng này có thể kích hoạt tối đa 1 lần mỗi 3 giây cho Đòn Phối Hợp cùng Thuộc Tính.</t>
         </is>
       </c>
     </row>
@@ -25843,11 +25843,11 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>&lt;size=40&gt;&lt;color=Title&gt;Basic Attack: True Sight - Conquest&lt;/color&gt;&lt;/size&gt;
-Khi ở trạng thái &lt;color=Highlight&gt;True Sight&lt;/color&gt;, nếu Changli sử dụng &lt;color=Highlight&gt;Ground Basic Attack&lt;/color&gt;, cô sẽ thi triển &lt;color=Highlight&gt;True Sight: Conquest&lt;/color&gt;, lao về phía kẻ địch và gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;, được tính là Sát Thương Resonance Skill. Sau khi thi triển &lt;color=Highlight&gt;True Sight: Conquest&lt;/color&gt;, trạng thái &lt;color=Highlight&gt;True Sight&lt;/color&gt; sẽ kết thúc.
+          <t>&lt;size=40&gt;&lt;color=Title&gt;Đòn Basic Attack: Chân Tướng - Chinh Phục&lt;/color&gt;&lt;/size&gt;
+Khi ở trạng thái &lt;color=Highlight&gt;Chân Tướng&lt;/color&gt;, nếu Changli sử dụng &lt;color=Highlight&gt;Đòn Basic Attack Trên Mặt Đất&lt;/color&gt;, cô sẽ thi triển &lt;color=Highlight&gt;Chân Tướng: Chinh Phục&lt;/color&gt;, lao về phía kẻ địch và gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;, được tính là Sát Thương Resonance Skill. Sau khi thi triển &lt;color=Highlight&gt;Chân Tướng: Chinh Phục&lt;/color&gt;, trạng thái &lt;color=Highlight&gt;Chân Tướng&lt;/color&gt; sẽ kết thúc.
 &lt;size=10&gt;&lt;/size&gt;
-&lt;size=40&gt;&lt;color=Title&gt;Basic Attack: True Sight - Charge&lt;/color&gt;&lt;/size&gt;
-Khi ở trạng thái &lt;color=Highlight&gt;True Sight&lt;/color&gt;, nếu Changli &lt;color=Highlight&gt;jumps&lt;/color&gt; hoặc sử dụng &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; trên không, cô sẽ thi triển &lt;color=Highlight&gt;True Sight: Charge&lt;/color&gt;, lao về phía kẻ địch và gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;, được tính là Sát Thương Resonance Skill. Sau khi thi triển &lt;color=Highlight&gt;True Sight: Charge&lt;/color&gt;, trạng thái &lt;color=Highlight&gt;True Sight&lt;/color&gt; sẽ kết thúc.</t>
+&lt;size=40&gt;&lt;color=Title&gt;Đòn Basic Attack: Chân Tướng - Tấn Công&lt;/color&gt;&lt;/size&gt;
+Khi ở trạng thái &lt;color=Highlight&gt;Chân Tướng&lt;/color&gt;, nếu Changli &lt;color=Highlight&gt;nhảy&lt;/color&gt; hoặc sử dụng &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; trên không, cô sẽ thi triển &lt;color=Highlight&gt;Chân Tướng: Tấn Công&lt;/color&gt;, lao về phía kẻ địch và gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;, được tính là Sát Thương Resonance Skill. Sau khi thi triển &lt;color=Highlight&gt;Chân Tướng: Tấn Công&lt;/color&gt;, trạng thái &lt;color=Highlight&gt;Chân Tướng&lt;/color&gt; sẽ kết thúc.</t>
         </is>
       </c>
     </row>
@@ -25916,9 +25916,9 @@
       <c r="M390" t="inlineStr">
         <is>
           <t>Changli có thể tích lũy tối đa 4 lớp Enflamement.
-Mỗi đòn Basic Attack: &lt;color=Highlight&gt;True Sight - Conquest&lt;/color&gt; trúng mục tiêu sẽ giúp Changli nhận 1 lớp Enflamement.
-Mỗi đòn Basic Attack: &lt;color=Highlight&gt;True Sight - Charge&lt;/color&gt; trúng mục tiêu sẽ giúp Changli nhận 1 lớp Enflamement.
-Mỗi đòn Resonance Liberation &lt;color=Highlight&gt;Radiance of Fealty&lt;/color&gt; sẽ giúp Changli nhận 4 lớp Enflamement.</t>
+Mỗi đòn Basic Attack: &lt;color=Highlight&gt;Thị Giác Chân Thật - Chinh Phục&lt;/color&gt; trúng mục tiêu sẽ giúp Changli nhận 1 lớp Enflamement.
+Mỗi đòn Basic Attack: &lt;color=Highlight&gt;Thị Giác Chân Thật - Tích Lực&lt;/color&gt; trúng mục tiêu sẽ giúp Changli nhận 1 lớp Enflamement.
+Mỗi đòn Resonance Liberation &lt;color=Highlight&gt;Hào Quang Trung Thành&lt;/color&gt; sẽ giúp Changli nhận 4 lớp Enflamement.</t>
         </is>
       </c>
     </row>
@@ -25987,9 +25987,9 @@
       <c r="M391" t="inlineStr">
         <is>
           <t>Verina có thể tích lũy tối đa 4 tầng Năng lượng Quang hợp.
-Verina nhận 1 tầng Năng lượng Quang hợp mỗi khi &lt;color=Highlight&gt;Basic Attack 5&lt;/color&gt; trúng mục tiêu.
-Verina nhận 1 tầng Năng lượng Quang hợp sau khi sử dụng Skill Cộng hưởng &lt;color=Highlight&gt;Botany Experiment&lt;/color&gt;.
-Verina nhận 1 tầng Năng lượng Quang hợp sau khi sử dụng Skill Khởi đầu &lt;color=Highlight&gt;Verdant Growth&lt;/color&gt;.</t>
+Verina nhận 1 tầng Năng lượng Quang hợp mỗi khi &lt;color=Highlight&gt;Đòn Basic Attack 5&lt;/color&gt; trúng mục tiêu.
+Verina nhận 1 tầng Năng lượng Quang hợp sau khi sử dụng Kỹ năng Cộng hưởng &lt;color=Highlight&gt;Thí nghiệm Thực vật&lt;/color&gt;.
+Verina nhận 1 tầng Năng lượng Quang hợp sau khi sử dụng Kỹ năng Khởi đầu &lt;color=Highlight&gt;Sự sinh trưởng Xanh tươi&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Khi Concerto Energy đạt tối đa, chuyển Resonator sẽ kích hoạt &lt;color=Highlight&gt;Outro Skill&lt;/color&gt; của Resonator hiện tại và tiêu hao toàn bộ Concerto Energy để kích hoạt &lt;color=Highlight&gt;Intro Skill&lt;/color&gt; của Resonator mới.</t>
+          <t>Khi Concerto Energy đạt tối đa, chuyển Resonator sẽ kích hoạt &lt;color=Highlight&gt;Kỹ Năng Outro&lt;/color&gt; của Resonator hiện tại và tiêu hao toàn bộ Concerto Energy để kích hoạt &lt;color=Highlight&gt;Kỹ Năng Intro&lt;/color&gt; của Resonator mới.</t>
         </is>
       </c>
     </row>
@@ -26120,8 +26120,8 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Khi Phoebe ở ngoài Vòng Gương, bất kỳ &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; hoặc &lt;color=Highlight&gt;Dodge Counter&lt;/color&gt; nào trúng Vòng Gương sẽ khúc xạ Light Thần Thánh, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; lên mục tiêu trong &lt;color=Highlight&gt;Ring of Mirrors&lt;/color&gt; và kéo chúng về trung tâm vòng. Sát thương gây ra được tính là Sát Thương Basic Attack. Có thể kích hoạt mỗi 0.5 giây.
-- Khi Phoebe ở trong Vòng Gương, &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; sẽ trở thành Basic Attack &lt;color=Highlight&gt;Chamuel's Star&lt;/color&gt;, thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;, được tính là Sát Thương Basic Attack.</t>
+          <t>Khi Phoebe ở ngoài Vòng Gương, bất kỳ &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; hoặc &lt;color=Highlight&gt;Dodge Counter Tránh&lt;/color&gt; nào trúng Vòng Gương sẽ khúc xạ Ánh Sáng Thần Thánh, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; lên mục tiêu trong &lt;color=Highlight&gt;Vòng Gương&lt;/color&gt; và kéo chúng về trung tâm vòng. DMG gây ra được tính là Sát Thương Đòn Basic Attack. Có thể kích hoạt mỗi 0.5 giây.
+- Khi Phoebe ở trong Vòng Gương, &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; sẽ trở thành Đòn Basic Attack &lt;color=Highlight&gt;Ngôi Sao Chamuel&lt;/color&gt;, thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;, được tính là Sát Thương Đòn Basic Attack.</t>
         </is>
       </c>
     </row>
@@ -26187,8 +26187,8 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>- Khi hiệu ứng Spectro Frazzle còn tồn tại, nó sẽ gây sát thương &lt;color=Light&gt;Spectro DMG&lt;/color&gt; định kỳ lên mục tiêu. Mục tiêu sẽ mất 1 lượt chồng hiệu ứng sau mỗi lần bị sát thương.
-- Sát thương của Spectro Frazzle tăng theo số lượt chồng hiệu ứng.</t>
+          <t>- Khi hiệu ứng Spectro Frazzle còn tồn tại, nó sẽ gây DMG &lt;color=Light&gt;Spectro&lt;/color&gt; định kỳ lên mục tiêu. Mục tiêu sẽ mất 1 lượt chồng hiệu ứng sau mỗi lần bị DMG.
+- DMG của Spectro Frazzle tăng theo số lượt chồng hiệu ứng.</t>
         </is>
       </c>
     </row>
@@ -26254,8 +26254,8 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>- Khi hiệu ứng Aero Erosion còn tồn tại, nó sẽ gây sát thương &lt;color=Wind&gt;Aero DMG&lt;/color&gt; định kỳ lên mục tiêu.
-- Sát thương của Aero Erosion tăng theo số lượt chồng hiệu ứng.</t>
+          <t>- Khi hiệu ứng Aero Erosion còn tồn tại, nó sẽ gây DMG &lt;color=Wind&gt;Aero&lt;/color&gt; định kỳ lên mục tiêu.
+- DMG của Aero Erosion tăng theo số lượt chồng hiệu ứng.</t>
         </is>
       </c>
     </row>
@@ -26323,10 +26323,10 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>- Glacio Chafe gây Glacio DMG khi tác động lên mục tiêu.
+          <t>- Glacio Chafe gây Sát Thương Glacio khi tác động lên mục tiêu.
 - Mỗi lớp Glacio Chafe sẽ làm giảm tốc độ di chuyển của mục tiêu.
 - Khi Glacio Chafe đạt tối đa, mục tiêu sẽ bị &lt;color=Highlight&gt;đóng băng&lt;/color&gt;, và tất cả các lớp Glacio Chafe sẽ bị loại bỏ. Cố gắng vùng vẫy để thoát khỏi trạng thái đóng băng nhanh hơn.
-- Glacio Chafe có thể tích lũy tối đa 10 lớp theo mặc định. Số lớp càng cao, sát thương gây ra càng lớn và thời gian &lt;color=Highlight&gt;đóng băng&lt;/color&gt; càng dài.</t>
+- Glacio Chafe có thể tích lũy tối đa 10 lớp theo mặc định. Số lớp càng cao, DMG gây ra càng lớn và thời gian &lt;color=Highlight&gt;đóng băng&lt;/color&gt; càng dài.</t>
         </is>
       </c>
     </row>
@@ -26392,8 +26392,8 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Khi Tích Lũy Nổ Cộng Hưởng đạt tối đa, tất cả lượt tích lũy sẽ bị xóa để kích hoạt &lt;color=Highlight&gt;explosion&lt;/color&gt;, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; lên mục tiêu và kẻ địch xung quanh.
-- Mặc định, Tích Lũy Nổ Cộng Hưởng có thể lên đến 10 lần. Số lượt tích lũy càng cao, sát thương gây ra càng lớn.</t>
+          <t>Khi Tích Lũy Nổ Cộng Hưởng đạt tối đa, tất cả lượt tích lũy sẽ bị xóa để kích hoạt &lt;color=Highlight&gt;vụ nổ&lt;/color&gt;, gây &lt;color=Fire&gt;Sát Thương Cộng Hưởng&lt;/color&gt; lên mục tiêu và kẻ địch xung quanh.
+- Mặc định, Tích Lũy Nổ Cộng Hưởng có thể lên đến 10 lần. Số lượt tích lũy càng cao, DMG gây ra càng lớn.</t>
         </is>
       </c>
     </row>
@@ -26528,10 +26528,10 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>- Khi hiệu ứng Electro Flare còn tồn tại, nó sẽ gây sát thương &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; định kỳ lên mục tiêu. Mục tiêu sẽ mất một nửa số lượt chồng hiệu ứng sau mỗi lần bị sát thương.
+          <t>- Khi hiệu ứng Electro Flare còn tồn tại, nó sẽ gây DMG &lt;color=Thunder&gt;Electro&lt;/color&gt; định kỳ lên mục tiêu. Mục tiêu sẽ mất một nửa số lượt chồng hiệu ứng sau mỗi lần bị DMG.
 - Khi Electro Flare đạt tối đa lượt chồng, bất kỳ lượt chồng mới nào gây ra sẽ chuyển thành Electro Rage có thể chồng thêm.
-- Electro Rage làm tăng sát thương của lần kích hoạt Electro Flare tiếp theo. Hiệu ứng này sẽ bị loại bỏ sau khi kích hoạt.
-- Electro Flare và Electro Rage có thể chồng tối đa 10 lần theo mặc định. Số lượt chồng càng cao, sát thương gây ra càng lớn.</t>
+- Electro Rage làm tăng DMG của lần kích hoạt Electro Flare tiếp theo. Hiệu ứng này sẽ bị loại bỏ sau khi kích hoạt.
+- Electro Flare và Electro Rage có thể chồng tối đa 10 lần theo mặc định. Số lượt chồng càng cao, DMG gây ra càng lớn.</t>
         </is>
       </c>
     </row>
@@ -26596,7 +26596,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Khi sử dụng Heavy Attack &lt;color=Highlight&gt;Absolution Litany&lt;/color&gt; hoặc Resonance Skill &lt;color=Highlight&gt;Utter Confession&lt;/color&gt;, hồi phục 60 Divine Giọng nói.</t>
+          <t>Khi sử dụng Đòn Heavy Attack &lt;color=Highlight&gt;Absolution Litany&lt;/color&gt; hoặc Resonance Skill &lt;color=Highlight&gt;Utter Confession&lt;/color&gt;, hồi phục 60 Divine Voice.</t>
         </is>
       </c>
     </row>
@@ -26666,10 +26666,10 @@
       <c r="M401" t="inlineStr">
         <is>
           <t>Roccia có thể chứa tối đa 300 Năng Lượng Sáng Tạo.
-- Gây Sát Thương bằng Normal Attack sẽ hồi phục Năng Lượng Sáng Tạo.
-- Giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để nạp đòn tiếp theo và hồi phục Năng Lượng Sáng Tạo.
-- Sử dụng Resonance Skill &lt;color=Highlight&gt;Acrobatic Trick&lt;/color&gt; sẽ hồi phục 100 Năng Lượng Sáng Tạo.
-- Sử dụng Kỹ Năng Giới Thiệu &lt;color=Highlight&gt;Pero, Help&lt;/color&gt; sẽ hồi phục 100 Năng Lượng Sáng Tạo.</t>
+- Gây Sát Thương bằng Đòn Normal Attack sẽ hồi phục Năng Lượng Sáng Tạo.
+- Giữ &lt;color=Highlight&gt;Đòn Normal Attack&lt;/color&gt; để nạp đòn tiếp theo và hồi phục Năng Lượng Sáng Tạo.
+- Sử dụng Resonance Skill &lt;color=Highlight&gt;Màn Nhào Lộn&lt;/color&gt; sẽ hồi phục 100 Năng Lượng Sáng Tạo.
+- Sử dụng Kỹ Năng Giới Thiệu &lt;color=Highlight&gt;Pero, Giúp Với&lt;/color&gt; sẽ hồi phục 100 Năng Lượng Sáng Tạo.</t>
         </is>
       </c>
     </row>
@@ -26735,7 +26735,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Khi Roccia đang ở trạng thái &lt;color=Highlight&gt;Beyond Imagination&lt;/color&gt; với ít nhất 100 Trí Tưởng, {Cus:Ipt,Touch=tap PC=press Gamepad=press} nút &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; để tiêu hao 100 Trí Tưởng và tung chiêu Basic Attack &lt;color=Highlight&gt;Thật sự Fantasy&lt;/color&gt;.
+          <t>Khi Roccia đang ở trạng thái &lt;color=Highlight&gt;Vượt Ngoài Trí Tưởng&lt;/color&gt; với ít nhất 100 Trí Tưởng, {Cus:Ipt,Touch=tap PC=press Gamepad=press} nút &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; để tiêu hao 100 Trí Tưởng và tung chiêu Basic Attack &lt;color=Highlight&gt;Ảo Ảnh Chân Thực&lt;/color&gt;.
 - Roccia sẽ thoát khỏi trạng thái này khi không còn ở trên không hoặc bị thay ra khỏi trận đấu.</t>
         </is>
       </c>
@@ -26809,13 +26809,13 @@
       <c r="M403" t="inlineStr">
         <is>
           <t>Carlotta có thể tích lũy tối đa 6 Tinh Thể Dẻo.
-- Không thể nhận Tinh Thể Dẻo khi đang trong trạng thái &lt;color=Highlight&gt;Twilight Tango&lt;/color&gt; kích hoạt bởi Resonance Liberation.
-- Hồi 3 Tinh Thể Dẻo khi sử dụng &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;.
-- Hồi 3 Tinh Thể Dẻo khi sử dụng &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt;.
-- Hồi 3 Tinh Thể Dẻo khi sử dụng Đòn Mid-air Attack &lt;color=Highlight&gt;Customary Greetings&lt;/color&gt;.
-- Hồi 3 Tinh Thể Dẻo khi sử dụng Intro Skill &lt;color=Highlight&gt;Wintertime Aria&lt;/color&gt;.
-- Hồi 3 Tinh Thể Dẻo khi sử dụng Resonance Skill &lt;color=Highlight&gt;Art of Violence&lt;/color&gt;.
-- Hồi 3 Tinh Thể Dẻo khi Dodge thành công &lt;color=Highlight&gt;Dodge&lt;/color&gt;.</t>
+- Không thể nhận Tinh Thể Dẻo khi đang trong trạng thái &lt;color=Highlight&gt;Điệu Tango Hoàng Hôn&lt;/color&gt; kích hoạt bởi Resonance Liberation.
+- Hồi 3 Tinh Thể Dẻo khi sử dụng &lt;color=Highlight&gt;Giai Đoạn 2 Đòn Basic Attack&lt;/color&gt;.
+- Hồi 3 Tinh Thể Dẻo khi sử dụng &lt;color=Highlight&gt;Đòn Tấn Công Mạnh&lt;/color&gt;.
+- Hồi 3 Tinh Thể Dẻo khi sử dụng Đòn Mid-air Attack &lt;color=Highlight&gt;Lời Chào Theo Thói Quen&lt;/color&gt;.
+- Hồi 3 Tinh Thể Dẻo khi sử dụng Kỹ Năng Khởi Động &lt;color=Highlight&gt;Khúc Aria Mùa Đông&lt;/color&gt;.
+- Hồi 3 Tinh Thể Dẻo khi sử dụng Resonance Skill &lt;color=Highlight&gt;Nghệ Thuật Bạo Lực&lt;/color&gt;.
+- Hồi 3 Tinh Thể Dẻo khi né tránh thành công &lt;color=Highlight&gt;Né Tránh&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26886,11 +26886,11 @@
       <c r="M404" t="inlineStr">
         <is>
           <t>Carlotta có thể tích lũy tối đa 120 điểm Chất.
-- Không thể nhận Chất khi đang trong trạng thái &lt;color=Highlight&gt;Twilight Tango&lt;/color&gt; kích hoạt bởi Resonance Liberation.
-- Hồi 30 điểm Chất khi sử dụng Intro Skill &lt;color=Highlight&gt;Wintertime Aria&lt;/color&gt;.
-- Hồi 10 điểm Chất cho mỗi 1 Tinh Thể Dẻo tiêu hao khi sử dụng Resonance Skill &lt;color=Highlight&gt;Chromatic Splendor&lt;/color&gt;.
-- Hồi 10 điểm Chất cho mỗi 1 Tinh Thể Dẻo tiêu hao khi sử dụng Basic Attack &lt;color=Highlight&gt;Necessary Measures&lt;/color&gt;.
-- Tiêu hao 1 Tinh Thể Dẻo và hồi 10 điểm Chất khi sử dụng &lt;color=Highlight&gt;Dodge Counter&lt;/color&gt;.</t>
+- Không thể nhận Chất khi đang trong trạng thái &lt;color=Highlight&gt;Điệu Tango Hoàng Hôn&lt;/color&gt; kích hoạt bởi Resonance Liberation.
+- Hồi 30 điểm Chất khi sử dụng Kỹ Năng Khởi Động &lt;color=Highlight&gt;Khúc Aria Mùa Đông&lt;/color&gt;.
+- Hồi 10 điểm Chất cho mỗi 1 Tinh Thể Dẻo tiêu hao khi sử dụng Resonance Skill &lt;color=Highlight&gt;Sắc Màu Rực Rỡ&lt;/color&gt;.
+- Hồi 10 điểm Chất cho mỗi 1 Tinh Thể Dẻo tiêu hao khi sử dụng Đòn Basic Attack &lt;color=Highlight&gt;Biện Pháp Cần Thiết&lt;/color&gt;.
+- Tiêu hao 1 Tinh Thể Dẻo và hồi 10 điểm Chất khi sử dụng &lt;color=Highlight&gt;Dodge Counter Tránh&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26955,7 +26955,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Gây sát thương lên mục tiêu đang bị &lt;color=Highlight&gt;Deconstruction&lt;/color&gt; sẽ bỏ qua 18% Phòng Ngự của chúng.</t>
+          <t>Gây DMG lên mục tiêu đang bị &lt;color=Highlight&gt;Phân Giải&lt;/color&gt; sẽ bỏ qua 18% Phòng Ngự của chúng.</t>
         </is>
       </c>
     </row>
@@ -27090,12 +27090,12 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>- &lt;color=Highlight&gt;Sweet Dream&lt;/color&gt;: Increase Hệ Số Sát Thương của &lt;color=Highlight&gt;Normal Attack&lt;/color&gt;, Basic Attack &lt;color=Highlight&gt;Vining Waltz&lt;/color&gt;, Basic Attack &lt;color=Highlight&gt;Blazing Waltz&lt;/color&gt;, Basic Attack &lt;color=Highlight&gt;Vining Ronde&lt;/color&gt;, Dodge Counter &lt;color=Highlight&gt;Atonement&lt;/color&gt;, Resonance Skill &lt;color=Highlight&gt;Crimson Blossom&lt;/color&gt; và Resonance Skill &lt;color=Highlight&gt;Floral Ravage&lt;/color&gt; lên 150%.
-- Khi sử dụng &lt;color=Highlight&gt;Ephemeral&lt;/color&gt;, tiêu hao toàn bộ Nụ Đỏ Thắm. Mỗi Nụ Đỏ Thắm tiêu hao sẽ tăng thêm Hệ Số Sát Thương của &lt;color=Highlight&gt;Sweet Dream&lt;/color&gt; lên 5%, tối đa 50%.
-- Khi ở &lt;color=Highlight&gt;Budding Mode&lt;/color&gt;, Camellya không thể nhận thêm Nụ Đỏ Thắm.
-- Khi ở &lt;color=Highlight&gt;Budding Mode&lt;/color&gt;, Hệ Số Energy Regen của &lt;color=Highlight&gt;Normal Attack&lt;/color&gt;, Basic Attack &lt;color=Highlight&gt;Vining Waltz&lt;/color&gt;, Basic Attack &lt;color=Highlight&gt;Blazing Waltz&lt;/color&gt;, Basic Attack &lt;color=Highlight&gt;Vining Ronde&lt;/color&gt;, Dodge Counter &lt;color=Highlight&gt;Atonement&lt;/color&gt;, Resonance Skill &lt;color=Highlight&gt;Crimson Blossom&lt;/color&gt; và Resonance Skill &lt;color=Highlight&gt;Floral Ravage&lt;/color&gt; giảm xuống 0%.
-- &lt;color=Highlight&gt;Budding Mode&lt;/color&gt; kết thúc khi Camellya rời khỏi trận đấu.
-- &lt;color=Highlight&gt;Budding Mode&lt;/color&gt; kết thúc khi toàn bộ Nhụy Đỏ Thắm bị tiêu hao hết.</t>
+          <t>- &lt;color=Highlight&gt;Giấc Mộng Ngọt Ngào&lt;/color&gt;: Tăng Hệ Số Sát Thương của &lt;color=Highlight&gt;Đòn Normal Attack&lt;/color&gt;, Đòn Basic Attack &lt;color=Highlight&gt;Điệu Vanxơ Dây Leo&lt;/color&gt;, Đòn Basic Attack &lt;color=Highlight&gt;Điệu Vanxơ Rực Lửa&lt;/color&gt;, Đòn Basic Attack &lt;color=Highlight&gt;Điệu Ronde Dây Leo&lt;/color&gt;, Dodge Counter Tránh &lt;color=Highlight&gt;Sám Hối&lt;/color&gt;, Resonance Skill &lt;color=Highlight&gt;Hoa Đỏ Thắm&lt;/color&gt; và Resonance Skill &lt;color=Highlight&gt;Tàn Phá Hoa Lệ&lt;/color&gt; lên 150%.
+- Khi sử dụng &lt;color=Highlight&gt;Phù Du&lt;/color&gt;, tiêu hao toàn bộ Nụ Đỏ Thắm. Mỗi Nụ Đỏ Thắm tiêu hao sẽ tăng thêm Hệ Số Sát Thương của &lt;color=Highlight&gt;Giấc Mộng Ngọt Ngào&lt;/color&gt; lên 5%, tối đa 50%.
+- Khi ở &lt;color=Highlight&gt;Chế Độ Nảy Mầm&lt;/color&gt;, Camellya không thể nhận thêm Nụ Đỏ Thắm.
+- Khi ở &lt;color=Highlight&gt;Chế Độ Nảy Mầm&lt;/color&gt;, Hệ Số Hồi Năng Lượng của &lt;color=Highlight&gt;Đòn Normal Attack&lt;/color&gt;, Đòn Basic Attack &lt;color=Highlight&gt;Điệu Vanxơ Dây Leo&lt;/color&gt;, Đòn Basic Attack &lt;color=Highlight&gt;Điệu Vanxơ Rực Lửa&lt;/color&gt;, Đòn Basic Attack &lt;color=Highlight&gt;Điệu Ronde Dây Leo&lt;/color&gt;, Dodge Counter Tránh &lt;color=Highlight&gt;Sám Hối&lt;/color&gt;, Resonance Skill &lt;color=Highlight&gt;Hoa Đỏ Thắm&lt;/color&gt; và Resonance Skill &lt;color=Highlight&gt;Tàn Phá Hoa Lệ&lt;/color&gt; giảm xuống 0%.
+- &lt;color=Highlight&gt;Chế Độ Nảy Mầm&lt;/color&gt; kết thúc khi Camellya rời khỏi trận đấu.
+- &lt;color=Highlight&gt;Chế Độ Nảy Mầm&lt;/color&gt; kết thúc khi toàn bộ Nhụy Đỏ Thắm bị tiêu hao hết.</t>
         </is>
       </c>
     </row>
@@ -27160,7 +27160,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Đánh trúng mục tiêu bằng Normal Attack sẽ tạo ra một &lt;color=Highlight&gt;Collapsed Core&lt;/color&gt;, sau 6 giây sẽ biến thành &lt;color=Highlight&gt;Flare Star Butterfly&lt;/color&gt;. &lt;color=Highlight&gt;Flare Star Butterflies&lt;/color&gt; sẽ tự động truy đuổi và tấn công mục tiêu, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;. Nếu đã có 5 &lt;color=Highlight&gt;Collapsed Cores&lt;/color&gt;, đòn &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; tiếp theo của Shorekeeper sẽ ngay lập tức biến một &lt;color=Highlight&gt;Collapsed Core&lt;/color&gt; thành &lt;color=Highlight&gt;Flare Star Butterfly&lt;/color&gt;.</t>
+          <t>Đánh trúng mục tiêu bằng Đòn Normal Attack sẽ tạo ra một &lt;color=Highlight&gt;Lõi Sụp Đổ&lt;/color&gt;, sau 6 giây sẽ biến thành &lt;color=Highlight&gt;Bướm Sao Lửa&lt;/color&gt;. &lt;color=Highlight&gt;Bướm Sao Lửa&lt;/color&gt; sẽ tự động truy đuổi và tấn công mục tiêu, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;. Nếu đã có 5 &lt;color=Highlight&gt;Lõi Sụp Đổ&lt;/color&gt;, đòn &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; tiếp theo của Shorekeeper sẽ ngay lập tức biến một &lt;color=Highlight&gt;Lõi Sụp Đổ&lt;/color&gt; thành &lt;color=Highlight&gt;Bướm Sao Lửa&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27359,11 +27359,11 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Khi ở trạng thái &lt;color=Highlight&gt;Intuition&lt;/color&gt;:
-- Nhận 3 Khối Siêu Lập Phương. Mỗi lần sử dụng Resonance Skill &lt;color=Highlight&gt;Law of Reigns&lt;/color&gt;, tiêu hao 1 Khối Siêu Lập Phương. &lt;color=Highlight&gt;Intuition&lt;/color&gt; kết thúc khi tất cả Khối Siêu Lập Phương bị tiêu hao.
-- &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; và &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; được thay thế bằng Basic Attack &lt;color=Highlight&gt;Pivot - Impale&lt;/color&gt;, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-- Resonance Skill &lt;color=Highlight&gt;Deduction&lt;/color&gt; trở thành Resonance Skill &lt;color=Highlight&gt;Divergence&lt;/color&gt;, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-- &lt;color=Highlight&gt;Dodge Counter&lt;/color&gt; trở thành Dodge Counter &lt;color=Highlight&gt;Unfathomed&lt;/color&gt;, gây Sát Thương Resonance Liberation.</t>
+          <t>Khi ở trạng thái &lt;color=Highlight&gt;Trực Giác&lt;/color&gt;:
+- Nhận 3 Khối Siêu Lập Phương. Mỗi lần sử dụng Resonance Skill &lt;color=Highlight&gt;Luật Của Vương Quyền&lt;/color&gt;, tiêu hao 1 Khối Siêu Lập Phương. &lt;color=Highlight&gt;Trực Giác&lt;/color&gt; kết thúc khi tất cả Khối Siêu Lập Phương bị tiêu hao.
+- &lt;color=Highlight&gt;Đòn Cơ Bản&lt;/color&gt; và &lt;color=Highlight&gt;Đòn Nặng&lt;/color&gt; được thay thế bằng Đòn Cơ Bản &lt;color=Highlight&gt;Xoay Chuyển - Đâm Xuyên&lt;/color&gt;, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
+- Resonance Skill &lt;color=Highlight&gt;Suy Luận&lt;/color&gt; trở thành Resonance Skill &lt;color=Highlight&gt;Phân Kỳ&lt;/color&gt;, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
+- &lt;color=Highlight&gt;Dodge Counter Tránh&lt;/color&gt; trở thành Dodge Counter Tránh &lt;color=Highlight&gt;Vô Tận&lt;/color&gt;, gây Sát Thương Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -27436,15 +27436,15 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>&lt;size=40&gt;&lt;color=Title&gt;Resonance Skill - Stroke of Genius&lt;/color&gt;&lt;/size&gt;
-Khi có &lt;color=Highlight&gt;Phatasmic Imprint&lt;/color&gt; ở gần, Resonance Skill của Zhezhi sẽ được thay thế bằng &lt;color=Highlight&gt;Stroke of Genius&lt;/color&gt;, có thể sử dụng khi đang ở trên không. Khi kích hoạt, Zhezhi sẽ:
-- Di chuyển đến vị trí của &lt;color=Highlight&gt;Phatasmic Imprint&lt;/color&gt;, loại bỏ nó và triệu hồi một Ivory Herald tấn công mục tiêu, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;, được tính là Sát Thương Basic Attack. Refresh số lần Dodge trên không nếu mục tiêu &lt;color=Highlight&gt;Phatasmic Imprint&lt;/color&gt; đang ở trên không.
+          <t>&lt;size=40&gt;&lt;color=Title&gt;Resonance Skill - Nét Thiên Tài&lt;/color&gt;&lt;/size&gt;
+Khi có &lt;color=Highlight&gt;Ấn Tượng Huyễn Tưởng&lt;/color&gt; ở gần, Resonance Skill của Zhezhi sẽ được thay thế bằng &lt;color=Highlight&gt;Nét Thiên Tài&lt;/color&gt;, có thể sử dụng khi đang ở trên không. Khi kích hoạt, Zhezhi sẽ:
+- Di chuyển đến vị trí của &lt;color=Highlight&gt;Ấn Tượng Huyễn Tưởng&lt;/color&gt;, loại bỏ nó và triệu hồi một Ivory Herald tấn công mục tiêu, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;, được tính là Sát Thương Basic Attack. Làm mới số lần Né Tránh trên không nếu mục tiêu &lt;color=Highlight&gt;Ấn Tượng Huyễn Tưởng&lt;/color&gt; đang ở trên không.
 - Nhận 1 tầng Thỏa Thích Họa Sĩ, kéo dài trong 8 giây và có thể tích lũy tối đa 2 tầng.
 &lt;size=10&gt;&lt;/size&gt;
-&lt;size=40&gt;&lt;color=Title&gt;Resonance Skill - Creation's Zenith&lt;/color&gt;&lt;/size&gt;
-Khi có &lt;color=Highlight&gt;Phantasmic Imprint&lt;/color&gt; ở gần và đang có 2 tầng Thỏa Thích Họa Sĩ, &lt;color=Highlight&gt;Stroke of Genius&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Creation's Zenith&lt;/color&gt;, có thể sử dụng khi đang ở trên không. Khi kích hoạt, Zhezhi sẽ:
+&lt;size=40&gt;&lt;color=Title&gt;Resonance Skill - Đỉnh Cao Sáng Tạo&lt;/color&gt;&lt;/size&gt;
+Khi có &lt;color=Highlight&gt;Ấn Tượng Huyễn Tưởng&lt;/color&gt; ở gần và đang có 2 tầng Thỏa Thích Họa Sĩ, &lt;color=Highlight&gt;Nét Thiên Tài&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Đỉnh Cao Sáng Tạo&lt;/color&gt;, có thể sử dụng khi đang ở trên không. Khi kích hoạt, Zhezhi sẽ:
 - Mất toàn bộ tầng Thỏa Thích Họa Sĩ
-- Di chuyển đến vị trí của &lt;color=Highlight&gt;Phantasmic Imprint&lt;/color&gt;, loại bỏ nó và triệu hồi một Ivory Herald tấn công mục tiêu, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; lớn hơn, được tính là Sát Thương Basic Attack, đồng thời tăng thêm 18% Sát Thương Basic Attack trong 27 giây. Refresh số lần Dodge trên không nếu mục tiêu &lt;color=Highlight&gt;Phatasmic Imprint&lt;/color&gt; đang ở trên không.</t>
+- Di chuyển đến vị trí của &lt;color=Highlight&gt;Ấn Tượng Huyễn Tưởng&lt;/color&gt;, loại bỏ nó và triệu hồi một Ivory Herald tấn công mục tiêu, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; lớn hơn, được tính là Sát Thương Basic Attack, đồng thời tăng thêm 18% Sát Thương Basic Attack trong 27 giây. Làm mới số lần Né Tránh trên không nếu mục tiêu &lt;color=Highlight&gt;Ấn Tượng Huyễn Tưởng&lt;/color&gt; đang ở trên không.</t>
         </is>
       </c>
     </row>
@@ -27576,9 +27576,9 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Zhezhi có thể chứa tối đa 90 Tần Số.
+          <t>Triết Chi có thể chứa tối đa 90 Tần Số.
 Tấn Công thông thường sẽ tích lũy Tần Số khi trúng mục tiêu.
-Kích hoạt Intro Skill sẽ tích lũy Tần Số.</t>
+Kích hoạt Kỹ Năng Khởi Động sẽ tích lũy Tần Số.</t>
         </is>
       </c>
     </row>
@@ -27644,8 +27644,8 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Normal Attack &lt;color=Highlight&gt;Zapstring's Dance&lt;/color&gt;, Resonance Liberation &lt;color=Highlight&gt;Thundering Wrath&lt;/color&gt; và Intro Skill &lt;color=Highlight&gt;Raging Storm&lt;/color&gt; sẽ áp dụng &lt;color=Highlight&gt;Sinner's Mark&lt;/color&gt; khi trúng đích.
-&lt;color=Highlight&gt;Sinner's Mark&lt;/color&gt; sẽ bị loại bỏ khi Yinlin rời khỏi chiến trường.</t>
+          <t>Đòn Normal Attack &lt;color=Highlight&gt;Điệu Nhảy Dây Điện&lt;/color&gt;, Resonance Liberation &lt;color=Highlight&gt;Thịnh Nộ Sấm Sét&lt;/color&gt; và Kỹ Năng Khởi Động &lt;color=Highlight&gt;Bão Tố Cuồng Nộ&lt;/color&gt; sẽ áp dụng &lt;color=Highlight&gt;Dấu Ấn Tội Nhân&lt;/color&gt; khi trúng đích.
+&lt;color=Highlight&gt;Dấu Ấn Tội Nhân&lt;/color&gt; sẽ bị loại bỏ khi Yinlin rời khỏi chiến trường.</t>
         </is>
       </c>
     </row>
@@ -27715,12 +27715,12 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Yinlin có thể tích lũy tối đa 100 Judgement Points. Cô kiếm Judgement Points qua các cách sau:
-Khi sử dụng Intro Skill &lt;color=Highlight&gt;Raging Storm&lt;/color&gt;;
-Khi Basic Attack &lt;color=Highlight&gt;Zapstring's Dance&lt;/color&gt; trúng mục tiêu;
-Khi sử dụng Resonance Skill &lt;color=Highlight&gt;Magnetic Roar&lt;/color&gt;;
-Khi Resonance Skill &lt;color=Highlight&gt;Electromagnetic Blast&lt;/color&gt; trúng mục tiêu;
-Khi sử dụng Resonance Skill &lt;color=Highlight&gt;Lightning Execution&lt;/color&gt;.</t>
+          <t>Ân Lâm có thể tích lũy tối đa 100 Điểm Phán Xét. Cô kiếm Điểm Phán Xét qua các cách sau:
+Khi sử dụng Kỹ Năng Khởi Động &lt;color=Highlight&gt;Bão Tố Cuồng Nộ&lt;/color&gt;;
+Khi Đòn Basic Attack &lt;color=Highlight&gt;Vũ Điệu Tia Lửa&lt;/color&gt; trúng mục tiêu;
+Khi sử dụng Resonance Skill &lt;color=Highlight&gt;Hống Gầm Từ Tính&lt;/color&gt;;
+Khi Resonance Skill &lt;color=Highlight&gt;Vụ Nổ Điện Từ&lt;/color&gt; trúng mục tiêu;
+Khi sử dụng Resonance Skill &lt;color=Highlight&gt;Hành Quyết Tia Chớp&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27787,7 +27787,7 @@
       <c r="M417" t="inlineStr">
         <is>
           <t>Khả năng chống gián đoạn của Jiyan tăng lên.
-- &lt;color=Highlight&gt;Basic Attack&lt;/color&gt;, &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; và &lt;color=Highlight&gt;Dodge Counter&lt;/color&gt; được thay thế bằng Heavy Attack &lt;color=Highlight&gt;Lance of Qingloong&lt;/color&gt;.</t>
+- &lt;color=Highlight&gt;Basic Attack&lt;/color&gt;, &lt;color=Highlight&gt;Tấn Công Mạnh&lt;/color&gt; và &lt;color=Highlight&gt;Dodge Counter Tránh&lt;/color&gt; được thay thế bằng Tấn Công Mạnh &lt;color=Highlight&gt;Lăng Kích Thanh Long&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27857,7 +27857,7 @@
         <is>
           <t>Jiyan có thể tích lũy tối đa 60 Điểm Quyết Tâm.
 Jiyan nhận Điểm Quyết Tâm khi Kỹ Năng Thường &lt;color=Highlight&gt;Lone Lance&lt;/color&gt; trúng mục tiêu.
-Jiyan nhận Điểm Quyết Tâm khi Intro Skill &lt;color=Highlight&gt;Tactical Strike&lt;/color&gt; trúng mục tiêu.
+Jiyan nhận Điểm Quyết Tâm khi Kỹ Năng Khởi Động &lt;color=Highlight&gt;Tactical Strike&lt;/color&gt; trúng mục tiêu.
 Điểm Quyết Tâm sẽ dần giảm nếu Jiyan không tấn công mục tiêu trong vòng 15 giây.</t>
         </is>
       </c>
@@ -27924,8 +27924,8 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Baizhi có thể giữ tối đa 4 điểm Concentration.
-Baizhi nhận được 1 điểm Concentration mỗi khi &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; trúng mục tiêu.</t>
+          <t>Baizhi có thể giữ tối đa 4 điểm Tập Trung.
+Baizhi nhận được 1 điểm Tập Trung mỗi khi &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -27995,12 +27995,12 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng &lt;color=Highlight&gt;Devastation&lt;/color&gt;, Rover bước vào trạng thái &lt;color=Highlight&gt;Dark Surge&lt;/color&gt;. Trong trạng thái này:
-- &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; được thay thế bằng &lt;color=Highlight&gt;Enhanced Basic Attack&lt;/color&gt;, thực hiện tối đa 5 đòn tấn công liên tiếp, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-- &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; được thay thế bằng &lt;color=Highlight&gt;Enhanced Heavy Attack&lt;/color&gt;;
-- Sử dụng &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; sau khi dùng &lt;color=Highlight&gt;Enhanced Heavy Attack&lt;/color&gt; để tung đòn &lt;color=Highlight&gt;Thwackblade&lt;/color&gt; tấn công mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;, được tính là sát thương Heavy Attack.
-- Sử dụng &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; sau khi dùng đòn &lt;color=Highlight&gt;Thwackblade&lt;/color&gt; để tung &lt;color=Highlight&gt;Enhanced Basic Attack 3&lt;/color&gt; tấn công mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;;
-- Resonance Skill &lt;color=Highlight&gt;Wingblade&lt;/color&gt; được thay thế bằng Resonance Skill &lt;color=Highlight&gt;Lifetaker&lt;/color&gt;, biến âm thanh thành lưỡi kiếm tấn công mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Sau khi sử dụng &lt;color=Highlight&gt;Tàn Phá&lt;/color&gt;, Rover bước vào trạng thái &lt;color=Highlight&gt;Sóng Âm U Ám&lt;/color&gt;. Trong trạng thái này:
+- &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; được thay thế bằng &lt;color=Highlight&gt;Đòn Basic Attack Nâng Cao&lt;/color&gt;, thực hiện tối đa 5 đòn tấn công liên tiếp, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
+- &lt;color=Highlight&gt;Đòn Heavy Attack&lt;/color&gt; được thay thế bằng &lt;color=Highlight&gt;Đòn Heavy Attack Nâng Cao&lt;/color&gt;;
+- Sử dụng &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; sau khi dùng &lt;color=Highlight&gt;Đòn Heavy Attack Nâng Cao&lt;/color&gt; để tung đòn &lt;color=Highlight&gt;Thwackblade&lt;/color&gt; tấn công mục tiêu, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;, được tính là DMG Đòn Heavy Attack.
+- Sử dụng &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; sau khi dùng đòn &lt;color=Highlight&gt;Thwackblade&lt;/color&gt; để tung &lt;color=Highlight&gt;Đòn Basic Attack Nâng Cao 3&lt;/color&gt; tấn công mục tiêu, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;;
+- Resonance Skill &lt;color=Highlight&gt;Wingblade&lt;/color&gt; được thay thế bằng Resonance Skill &lt;color=Highlight&gt;Lifetaker&lt;/color&gt;, biến âm thanh thành lưỡi kiếm tấn công mục tiêu, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28065,7 +28065,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Có thể kích nổ bằng Heavy Attack &lt;color=Highlight&gt;Detonate&lt;/color&gt;, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.</t>
+          <t>Có thể kích nổ bằng Đòn Heavy Attack &lt;color=Highlight&gt;Kích Nổ&lt;/color&gt;, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28130,7 +28130,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Có thể kích nổ bằng Heavy Attack &lt;color=Highlight&gt;Detonate&lt;/color&gt;, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.</t>
+          <t>Có thể kích nổ bằng Đòn Heavy Attack &lt;color=Highlight&gt;Kích Nổ&lt;/color&gt;, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28195,7 +28195,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Có thể kích nổ bằng Heavy Attack &lt;color=Highlight&gt;Detonate&lt;/color&gt;, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.</t>
+          <t>Có thể kích nổ bằng Đòn Heavy Attack &lt;color=Highlight&gt;Kích Nổ&lt;/color&gt;, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28262,9 +28262,9 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Khi Resonator chủ động tấn công bằng &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; trúng mục tiêu, Mortefi sẽ thực hiện Attack Phối Hợp, bắn ra 1 &lt;color=Highlight&gt;Marcato&lt;/color&gt;.
-Khi Resonator chủ động tấn công bằng &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; trúng mục tiêu, Mortefi sẽ thực hiện Attack Phối Hợp, bắn ra 2 &lt;color=Highlight&gt;Marcato&lt;/color&gt;.
-Mortefi có thể thực hiện Attack Phối Hợp mỗi 0.35 giây.</t>
+          <t>Khi Resonator chủ động tấn công bằng &lt;color=Highlight&gt;Đòn Cơ Bản&lt;/color&gt; trúng mục tiêu, Mortefi sẽ thực hiện Tấn Công Phối Hợp, bắn ra 1 &lt;color=Highlight&gt;Marcato&lt;/color&gt;.
+Khi Resonator chủ động tấn công bằng &lt;color=Highlight&gt;Đòn Nặng&lt;/color&gt; trúng mục tiêu, Mortefi sẽ thực hiện Tấn Công Phối Hợp, bắn ra 2 &lt;color=Highlight&gt;Marcato&lt;/color&gt;.
+Mortefi có thể thực hiện Tấn Công Phối Hợp mỗi 0.35 giây.</t>
         </is>
       </c>
     </row>
@@ -28331,7 +28331,7 @@
       <c r="M425" t="inlineStr">
         <is>
           <t>Danjin có thể tích lũy tối đa 120 Hoa Hồng Đỏ.
-Danjin nhận được Hoa Hồng Đỏ khi sử dụng Resonance Skill &lt;color=Highlight&gt;Crimson Fragment&lt;/color&gt;.</t>
+Danjin nhận được Hoa Hồng Đỏ khi sử dụng Resonance Skill &lt;color=Highlight&gt;Mảnh Đỏ Thẫm&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28396,7 +28396,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Khi Danjin tấn công mục tiêu bằng &lt;color=Highlight&gt;Incinerating Will&lt;/color&gt; của Resonance Skill, sát thương gây ra tăng 20%.</t>
+          <t>Khi Danjin tấn công mục tiêu bằng &lt;color=Highlight&gt;Ý Chí Thiêu Đốt&lt;/color&gt; của Resonance Skill, sát thương gây ra tăng 20%.</t>
         </is>
       </c>
     </row>
@@ -28464,10 +28464,10 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Chixia có thể mang theo tối đa 60 Viên Thermobaric Bullets.
-Skill Nội Tại &lt;color=Highlight&gt;Scorching Magazine&lt;/color&gt; tăng số Viên Thermobaric Bullets tối đa thêm 10.
-Chixia nhận được Viên Thermobaric Bullets mỗi khi Normal Attack &lt;color=Highlight&gt;POW POW&lt;/color&gt; trúng mục tiêu.
-Chixia nhận được Viên Thermobaric Bullets khi sử dụng Intro Skill &lt;color=Highlight&gt;Grand Entrance&lt;/color&gt; và Resonance Skill &lt;color=Highlight&gt;Whizzing Fight Spirit&lt;/color&gt;.</t>
+          <t>Chixia có thể mang theo tối đa 60 Viên Đạn Nhiệt Áp.
+Kỹ năng Nội Tại &lt;color=Highlight&gt;Kho Đạn Nóng Bỏng&lt;/color&gt; tăng số Viên Đạn Nhiệt Áp tối đa thêm 10.
+Chixia nhận được Viên Đạn Nhiệt Áp mỗi khi tấn công thường &lt;color=Highlight&gt;POW POW&lt;/color&gt; trúng mục tiêu.
+Chixia nhận được Viên Đạn Nhiệt Áp khi sử dụng Kỹ Năng Khởi Động &lt;color=Highlight&gt;Lối Vào Hoành Tráng&lt;/color&gt; và Resonance Skill &lt;color=Highlight&gt;Tinh Thần Chiến Đấu Vèo Vèo&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28537,10 +28537,10 @@
       <c r="M428" t="inlineStr">
         <is>
           <t>Jianxin có thể chứa tối đa 120 Chi.
-Chi thu được khi Normal Attack &lt;color=Highlight&gt;Fengyiquan&lt;/color&gt; trúng mục tiêu.
-Chi thu được khi Resonance Skill &lt;color=Highlight&gt;Calming Air&lt;/color&gt; được kích hoạt.
-Chi thu được khi Resonance Skill &lt;color=Highlight&gt;Chi Counter&lt;/color&gt; hoặc &lt;color=Highlight&gt;Chi Parry&lt;/color&gt; trúng mục tiêu.
-Chi thu được khi Intro Skill &lt;color=Highlight&gt;Essence of Ta&lt;/color&gt; trúng mục tiêu.</t>
+Chi thu được khi Normal Attack &lt;color=Highlight&gt;Phong Ý Quyền&lt;/color&gt; trúng mục tiêu.
+Chi thu được khi Resonance Skill &lt;color=Highlight&gt;Gió Lặng&lt;/color&gt; được kích hoạt.
+Chi thu được khi Resonance Skill &lt;color=Highlight&gt;Phản Công Chi&lt;/color&gt; hoặc &lt;color=Highlight&gt;Phòng Thủ Chi&lt;/color&gt; trúng mục tiêu.
+Chi thu được khi Kỹ Năng Khởi Động &lt;color=Highlight&gt;Bản Chất Đạo&lt;/color&gt; trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -28736,8 +28736,8 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Sau &lt;color=Highlight&gt;Antique&lt;/color&gt;, Youhu nhận được một &lt;color=Highlight&gt;Lucky Draw&lt;/color&gt; ngẫu nhiên. Khi có &lt;color=Highlight&gt;Antique&lt;/color&gt;, &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; tiếp theo của cô sẽ kích hoạt &lt;color=Highlight&gt;Antique Appraisal&lt;/color&gt; tương ứng.
-Mỗi lần chỉ có thể giữ một &lt;color=Highlight&gt;Antique&lt;/color&gt;, và &lt;color=Highlight&gt;Antique&lt;/color&gt; mới rút sẽ thay thế cho cái hiện có.</t>
+          <t>Sau &lt;color=Highlight&gt;Rút Thăm May Mắn&lt;/color&gt;, Youhu nhận được một &lt;color=Highlight&gt;Cổ Vật&lt;/color&gt; ngẫu nhiên. Khi có &lt;color=Highlight&gt;Cổ Vật&lt;/color&gt;, &lt;color=Highlight&gt;Đòn Cơ Bản&lt;/color&gt; tiếp theo của cô sẽ kích hoạt &lt;color=Highlight&gt;Định Giá Cổ Vật&lt;/color&gt; tương ứng.
+Mỗi lần chỉ có thể giữ một &lt;color=Highlight&gt;Cổ Vật&lt;/color&gt;, và &lt;color=Highlight&gt;Cổ Vật&lt;/color&gt; mới rút sẽ thay thế cho cái hiện có.</t>
         </is>
       </c>
     </row>
@@ -28803,8 +28803,8 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Với một &lt;color=Highlight&gt;Antique&lt;/color&gt;, &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; tiếp theo của Youhu sẽ kích hoạt &lt;color=Highlight&gt;Antique Appraisal&lt;/color&gt; tương ứng.
-Chỉ có thể tồn tại một &lt;color=Highlight&gt;Antique&lt;/color&gt; tại một thời điểm, và &lt;color=Highlight&gt;Antique&lt;/color&gt; mới rút sẽ thay thế cái hiện có.</t>
+          <t>Với một &lt;color=Highlight&gt;Đồ Cổ&lt;/color&gt;, &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; tiếp theo của Youhu sẽ kích hoạt &lt;color=Highlight&gt;Đánh Giá Đồ Cổ&lt;/color&gt; tương ứng.
+Chỉ có thể tồn tại một &lt;color=Highlight&gt;Đồ Cổ&lt;/color&gt; tại một thời điểm, và &lt;color=Highlight&gt;Đồ Cổ&lt;/color&gt; mới rút sẽ thay thế cái hiện có.</t>
         </is>
       </c>
     </row>
@@ -28869,7 +28869,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Khi nhân vật chủ động trong đội bị tấn công, 1 Shield Rocksteady sẽ được tiêu hao để giảm Sát Thương nhận vào.</t>
+          <t>Khi nhân vật chủ động trong đội bị tấn công, 1 Khiên Rocksteady sẽ được tiêu hao để giảm Sát Thương nhận vào.</t>
         </is>
       </c>
     </row>
@@ -28935,8 +28935,8 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Khi Aalto đi qua Sương Mù hoặc Cánh Gate of Quandary, cậu sẽ bước vào trạng thái &lt;color=Highlight&gt;Mistcloak Dash&lt;/color&gt;.
-- Khi &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; hoặc &lt;color=Highlight&gt;Mid-air Attack&lt;/color&gt; xuyên qua Sương Mù và trúng mục tiêu, sẽ hồi phục 1 Giọt Sương.</t>
+          <t>Khi Aalto đi qua Sương Mù hoặc Cánh Cổng Băn Khoăn, cậu sẽ bước vào trạng thái &lt;color=Highlight&gt;Đột Phá Bằng Áo Choàng Sương&lt;/color&gt;.
+- Khi &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; hoặc &lt;color=Highlight&gt;Đòn Tấn Công Giữa Không&lt;/color&gt; xuyên qua Sương Mù và trúng mục tiêu, sẽ hồi phục 1 Giọt Sương.</t>
         </is>
       </c>
     </row>
@@ -29001,7 +29001,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Khi Aalto đi qua Sương Mù hoặc Cổng Lưỡng Nan, cậu sẽ bước vào trạng thái &lt;color=Highlight&gt;Mistcloak Dash&lt;/color&gt;.</t>
+          <t>Khi Aalto đi qua Sương Mù hoặc Cổng Lưỡng Nan, cậu sẽ bước vào trạng thái &lt;color=Highlight&gt;Đột Phá Sương Mù&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -29070,8 +29070,8 @@
       <c r="M436" t="inlineStr">
         <is>
           <t>Brant có thể chứa tối đa 100 Bravo.
-- Nhận Bravo khi Tấn Công Thường trúng mục tiêu.
-- Nhận Bravo khi Intro Skill trúng mục tiêu.
+- Nhận Bravo khi Normal Attack trúng mục tiêu.
+- Nhận Bravo khi Kỹ Năng Khởi Động trúng mục tiêu.
 - Nhận Bravo khi Resonance Skill trúng mục tiêu.</t>
         </is>
       </c>
@@ -29137,7 +29137,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Tỷ lệ nhận Bravo tăng 100% khi &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; hoặc Resonance Skill &lt;color=Highlight&gt;Anchors Aweigh!&lt;/color&gt; trúng mục tiêu. Đồng thời, Forte Circuit &lt;color=Highlight&gt;Theatrical Moment&lt;/color&gt; được thay thế bằng &lt;color=Highlight&gt;"My" Moment&lt;/color&gt;.</t>
+          <t>Tỷ lệ nhận Bravo tăng 100% khi &lt;color=Highlight&gt;Đòn Normal Attack&lt;/color&gt; hoặc Resonance Skill &lt;color=Highlight&gt;Thả Neo!&lt;/color&gt; trúng mục tiêu. Đồng thời, Forte Circuit &lt;color=Highlight&gt;Khoảnh Khắc Sân Khấu&lt;/color&gt; được thay thế bằng &lt;color=Highlight&gt;Khoảnh Khắc "Của Tôi"&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -29202,7 +29202,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Brant nhận thêm Tấn Công dựa trên Tái Tạo Năng Lượng: Cứ mỗi 1% Tái Tạo Năng Lượng vượt quá 150%, Brant nhận thêm 12 điểm Tấn Công, tối đa 1560.</t>
+          <t>Brant nhận thêm ATK dựa trên Tái Tạo Năng Lượng: Cứ mỗi 1% Tái Tạo Năng Lượng vượt quá 150%, Brant nhận thêm 12 điểm ATK, tối đa 1560.</t>
         </is>
       </c>
     </row>
@@ -29267,7 +29267,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Heal toàn bộ Resonators gần đó trong đội khi chỉ số Bravo đạt 25, 50, 75 và 100.</t>
+          <t>Hồi phục toàn bộ Resonator gần đó trong đội khi chỉ số Bravo đạt 25, 50, 75 và 100.</t>
         </is>
       </c>
     </row>
@@ -29339,14 +29339,14 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>- &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; chuyển thành &lt;color=Highlight&gt;Phantom Sting&lt;/color&gt; – Đòn Đâm Ma. Thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;. Có thể sử dụng khi đang bay. Khi sử dụng trên không, &lt;color=Highlight&gt;Phantom Sting&lt;/color&gt; sẽ tiêu hao STA và combo không bị reset khi Cantarella ở trên không.
-- Đánh trúng mục tiêu bằng &lt;color=Highlight&gt;Phantom Sting&lt;/color&gt; sẽ tiêu hao 1 điểm Trance để nhận 1 điểm Shiver và hồi phục cho tất cả Resonators gần đó trong đội.
-- Đòn thứ ba của &lt;color=Highlight&gt;Phantom Sting&lt;/color&gt; kích hoạt 3 Đòn Phối Hợp, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-- &lt;color=Highlight&gt;Mid-air Attack&lt;/color&gt; chuyển thành &lt;color=Highlight&gt;Abysmal Vortex&lt;/color&gt;. {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Nhảy&lt;/color&gt; để thực hiện Đòn Lao Xuống, tiêu hao STA và gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-- &lt;color=Highlight&gt;Dodge Counter&lt;/color&gt; chuyển thành &lt;color=Highlight&gt;Shadowy Sweep&lt;/color&gt;. Tấn công mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;. {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng để kích hoạt &lt;color=Highlight&gt;Phantom Sting Stage 2&lt;/color&gt;.
-- Khi &lt;color=Highlight&gt;Abysmal Vortex&lt;/color&gt; hoặc &lt;color=Highlight&gt;Shadowy Sweep&lt;/color&gt; trúng mục tiêu, tiêu hao 1 điểm Trance để nhận 1 điểm Shiver và hồi phục cho tất cả Resonators gần đó trong đội.
+          <t>- &lt;color=Highlight&gt;Đòn Cơ Bản&lt;/color&gt; chuyển thành &lt;color=Highlight&gt;Phantom Sting&lt;/color&gt; – Đòn Đâm Ma. Thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;. Có thể sử dụng khi đang bay. Khi sử dụng trên không, &lt;color=Highlight&gt;Phantom Sting&lt;/color&gt; sẽ tiêu hao STA và combo không bị reset khi Cantarella ở trên không.
+- Đánh trúng mục tiêu bằng &lt;color=Highlight&gt;Phantom Sting&lt;/color&gt; sẽ tiêu hao 1 điểm Trance để nhận 1 điểm Shiver và hồi phục cho tất cả Resonator gần đó trong đội.
+- Đòn thứ ba của &lt;color=Highlight&gt;Phantom Sting&lt;/color&gt; kích hoạt 3 Đòn Phối Hợp, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
+- &lt;color=Highlight&gt;Đòn Trên Không&lt;/color&gt; chuyển thành &lt;color=Highlight&gt;Abysmal Vortex&lt;/color&gt;. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Nhảy&lt;/color&gt; để thực hiện Đòn Lao Xuống, tiêu hao STA và gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
+- &lt;color=Highlight&gt;Dodge Counter Tránh&lt;/color&gt; chuyển thành &lt;color=Highlight&gt;Shadowy Sweep&lt;/color&gt;. Tấn công mục tiêu, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Đòn Cơ Bản&lt;/color&gt; ngay sau khi sử dụng kỹ năng để kích hoạt &lt;color=Highlight&gt;Phantom Sting Giai Đoạn 2&lt;/color&gt;.
+- Khi &lt;color=Highlight&gt;Abysmal Vortex&lt;/color&gt; hoặc &lt;color=Highlight&gt;Shadowy Sweep&lt;/color&gt; trúng mục tiêu, tiêu hao 1 điểm Trance để nhận 1 điểm Shiver và hồi phục cho tất cả Resonator gần đó trong đội.
 - Ảo ảnh kéo dài trong 8 giây.
-- &lt;color=Highlight&gt;Mirage&lt;/color&gt; sẽ kết thúc khi Trance cạn kiệt.</t>
+- &lt;color=Highlight&gt;Ảo ảnh&lt;/color&gt; sẽ kết thúc khi Trance cạn kiệt.</t>
         </is>
       </c>
     </row>
@@ -29413,9 +29413,9 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Giảm tốc độ di chuyển của mục tiêu trong 6,5 giây. Khi mục tiêu chịu sát thương, &lt;color=Highlight&gt;Giật Mạch&lt;/color&gt; sẽ kích hoạt một lần, loại bỏ &lt;color=Highlight&gt;Hazy Dream&lt;/color&gt; để gây &lt;color=Dark&gt;Sát Thương Hỗn Loạn&lt;/color&gt;, được tính là sát thương từ Basic Attack.
-Các đòn tấn công từ Resonators khác trong đội sẽ không &lt;color=Highlight&gt;Giật Mạch&lt;/color&gt; mục tiêu đang chịu ảnh hưởng của &lt;color=Highlight&gt;Hazy Dream&lt;/color&gt; và sẽ loại bỏ hiệu ứng này.
-Đòn Phối Hợp và sát thương từ Kỹ Năng Hỗ Trợ sẽ không kích hoạt &lt;color=Highlight&gt;Giật Mạch&lt;/color&gt;.</t>
+          <t>Giảm tốc độ di chuyển của mục tiêu trong 6,5 giây. Khi mục tiêu chịu DMG, &lt;color=Highlight&gt;Giật Mạch&lt;/color&gt; sẽ kích hoạt một lần, loại bỏ &lt;color=Highlight&gt;Giấc Mơ Mơ Hồ&lt;/color&gt; để gây &lt;color=Dark&gt;Sát Thương Hỗn Loạn&lt;/color&gt;, được tính là DMG từ Đòn Cơ Bản.
+Các đòn tấn công từ Resonator khác trong đội sẽ không &lt;color=Highlight&gt;Giật Mạch&lt;/color&gt; mục tiêu đang chịu ảnh hưởng của &lt;color=Highlight&gt;Giấc Mơ Mơ Hồ&lt;/color&gt; và sẽ loại bỏ hiệu ứng này.
+Đòn Phối Hợp và DMG từ Kỹ Năng Hỗ Trợ sẽ không kích hoạt &lt;color=Highlight&gt;Giật Mạch&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -29484,9 +29484,9 @@
       <c r="M442" t="inlineStr">
         <is>
           <t>Rover có thể giữ tối đa 120 Sợi Gió.
-Mỗi giai đoạn của Mid-air Attack &lt;color=Highlight&gt;Cloudburst Dance&lt;/color&gt; hồi 25 Sợi Gió khi trúng mục tiêu.
-Thi triển &lt;color=Highlight&gt;Intro Skill&lt;/color&gt; hồi 20 Sợi Gió.
-Đánh trúng mục tiêu bằng &lt;color=Highlight&gt;Basic Attack Stage 3 or 4&lt;/color&gt; hoặc &lt;color=Highlight&gt;Dodge Counter&lt;/color&gt; hồi 10 Sợi Gió.</t>
+Mỗi giai đoạn của Kỹ Năng Mid-air Attack &lt;color=Highlight&gt;Điệu Nhảy Mây Đen&lt;/color&gt; hồi 25 Sợi Gió khi trúng mục tiêu.
+Thi triển &lt;color=Highlight&gt;Kỹ Năng Khởi Động&lt;/color&gt; hồi 20 Sợi Gió.
+Đánh trúng mục tiêu bằng &lt;color=Highlight&gt;Giai Đoạn 3 hoặc 4 của Kỹ Năng Basic Attack&lt;/color&gt; hoặc &lt;color=Highlight&gt;Dodge Counter Tránh&lt;/color&gt; hồi 10 Sợi Gió.</t>
         </is>
       </c>
     </row>
@@ -29551,7 +29551,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Tấn Công của Resonators nhặt Euphonia tăng 15% trong 20 giây.</t>
+          <t>ATK của Resonator nhặt Euphonia tăng 15% trong 20 giây.</t>
         </is>
       </c>
     </row>
@@ -29623,14 +29623,14 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Khi ở trạng thái &lt;color=Highlight&gt;Striding Lion&lt;/color&gt;:
-- Có thể tấn công giữa không trung. Nếu Lingyang đứng trên mặt đất, dùng Heavy Attack &lt;color=Highlight&gt;Glorious Plunge&lt;/color&gt; để bay lên.
-- Lion's Spirit sẽ bị tiêu hao liên tục trong 5 giây trước khi cạn kiệt, và khi cạn kiệt, trạng thái &lt;color=Highlight&gt;Striding Lion&lt;/color&gt; sẽ kết thúc;
-- Nếu Lingyang đang ở trạng thái Resonance Liberation &lt;color=Highlight&gt;Lion's Vigor&lt;/color&gt;, tốc độ tiêu hao Lion's Spirit giảm 50%, kéo dài trạng thái &lt;color=Highlight&gt;Striding Lion&lt;/color&gt; thêm tối đa 10 giây.
-- &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; của Lingyang được thay thế bằng Basic Attack &lt;color=Highlight&gt;Feral Gyrate&lt;/color&gt;, thực hiện tối đa 2 đòn tấn công liên tiếp, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;;
-- &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; của Lingyang được thay thế bằng &lt;color=Highlight&gt;Mountain Roamer&lt;/color&gt;, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;;
-- Khi Lion's Spirit dưới 10, dùng &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Stormy Kicks&lt;/color&gt;, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;; sau khi thực hiện Basic Attack &lt;color=Highlight&gt;Stormy Kicks&lt;/color&gt;, Đòn Mid-air Attack &lt;color=Highlight&gt;Tail Strike&lt;/color&gt; sẽ khả dụng.
-- Concerto Energy được hồi phục khi Lion's Spirit bị tiêu hao.</t>
+          <t>Khi ở trạng thái &lt;color=Highlight&gt;Sư Tử Vươn Mình&lt;/color&gt;:
+- Có thể tấn công giữa không trung. Nếu Lingyang đứng trên mặt đất, dùng Đòn Tấn Công Mạnh &lt;color=Highlight&gt;Lao Dũng Mãnh&lt;/color&gt; để bay lên.
+- Linh Khí Sư Tử sẽ bị tiêu hao liên tục trong 5 giây trước khi cạn kiệt, và khi cạn kiệt, trạng thái &lt;color=Highlight&gt;Sư Tử Vươn Mình&lt;/color&gt; sẽ kết thúc;
+- Nếu Lingyang đang ở trạng thái Resonance Liberation &lt;color=Highlight&gt;Sức Mạnh Sư Tử&lt;/color&gt;, tốc độ tiêu hao Linh Khí Sư Tử giảm 50%, kéo dài trạng thái &lt;color=Highlight&gt;Sư Tử Vươn Mình&lt;/color&gt; thêm tối đa 10 giây.
+- &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; của Lingyang được thay thế bằng Đòn Basic Attack &lt;color=Highlight&gt;Xoay Thân Hoang Dã&lt;/color&gt;, thực hiện tối đa 2 đòn tấn công liên tiếp, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;;
+- &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; của Lingyang được thay thế bằng &lt;color=Highlight&gt;Kẻ Lang Thang Núi Rừng&lt;/color&gt;, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;;
+- Khi Linh Khí Sư Tử dưới 10, dùng &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Đòn Đá Bão Táp&lt;/color&gt;, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;; sau khi thực hiện Đòn Basic Attack &lt;color=Highlight&gt;Đòn Đá Bão Táp&lt;/color&gt;, Đòn Tấn Công Giữa Không &lt;color=Highlight&gt;Vỗ Đuôi&lt;/color&gt; sẽ khả dụng.
+- Concerto Energy được hồi phục khi Linh Khí Sư Tử bị tiêu hao.</t>
         </is>
       </c>
     </row>
@@ -29698,7 +29698,7 @@
       <c r="M445" t="inlineStr">
         <is>
           <t>Tối đa 2 &lt;color=Highlight&gt;Ensemble Sylphs&lt;/color&gt; có thể tồn tại đồng thời.
-Nếu Basic Attack Stage 4 của Ciaccona bị gián đoạn, &lt;color=Highlight&gt;Ensemble Sylphs&lt;/color&gt; tạo ra sẽ hoàn thành hành động thay Ciaccona và đưa cô vào trạng thái &lt;color=Highlight&gt;Solo Concert&lt;/color&gt;.
+Nếu Đòn Basic Attack Giai Đoạn 4 của Ciaccona bị gián đoạn, &lt;color=Highlight&gt;Ensemble Sylphs&lt;/color&gt; tạo ra sẽ hoàn thành hành động thay Ciaccona và đưa cô vào trạng thái &lt;color=Highlight&gt;Solo Concert&lt;/color&gt;.
 Nếu &lt;color=Highlight&gt;Solo Concert&lt;/color&gt; của Ciaccona bị gián đoạn, &lt;color=Highlight&gt;Ensemble Sylphs&lt;/color&gt; tạo ra sẽ tiếp tục &lt;color=Highlight&gt;Solo Concert&lt;/color&gt; thay cô.</t>
         </is>
       </c>
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Khi Ciaccona hoặc Ensemble Sylph biểu diễn Solo Concert, họ sẽ tăng 24% Aero DMG cho tất cả Resonators trong đội ở gần. Hiệu ứng này không thể chồng chất.</t>
+          <t>Khi Ciaccona hoặc Ensemble Sylph biểu diễn Solo Concert, họ sẽ tăng 24% Sát Thương Aero cho tất cả Resonator trong đội ở gần. Hiệu ứng này không thể chồng chất.</t>
         </is>
       </c>
     </row>
@@ -29831,7 +29831,7 @@
       <c r="M447" t="inlineStr">
         <is>
           <t>Ciaccona có thể giữ tối đa 3 đoạn Bản Chất Âm Nhạc.
-Sử dụng &lt;color=Highlight&gt;Basic Attack Stage 4&lt;/color&gt; và &lt;color=Highlight&gt;Intro Skill&lt;/color&gt; sẽ hồi phục 1 đoạn Bản Chất Âm Nhạc.</t>
+Sử dụng &lt;color=Highlight&gt;Đòn Basic Attack Giai Đoạn 4&lt;/color&gt; và &lt;color=Highlight&gt;Kỹ Năng Intro&lt;/color&gt; sẽ hồi phục 1 đoạn Bản Chất Âm Nhạc.</t>
         </is>
       </c>
     </row>
@@ -29896,7 +29896,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Khi Vibration Strength cạn kiệt, kẻ địch sẽ bị &lt;color=Highlight&gt;Immobilized&lt;/color&gt; và không thể thực hiện bất kỳ hành động nào trong một khoảng thời gian.</t>
+          <t>Khi Sức Rung cạn kiệt, kẻ địch sẽ bị &lt;color=Highlight&gt;Bất Động&lt;/color&gt; và không thể thực hiện bất kỳ hành động nào trong một khoảng thời gian.</t>
         </is>
       </c>
     </row>
@@ -29966,12 +29966,12 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Zani có thể chứa tối đa 100 Redundant Energy.
-Nhận Redundant Energy khi Tấn Công Thường trúng mục tiêu.
-Nhận Redundant Energy khi Intro Skill &lt;color=Highlight&gt;Immediate Execution&lt;/color&gt; trúng mục tiêu.
-Nhận Redundant Energy khi sử dụng Resonance Skill &lt;color=Highlight&gt;Tiêu Chuẩn Defense Protocol&lt;/color&gt;.
-Nhận Redundant Energy khi sử dụng Resonance Skill &lt;color=Highlight&gt;Pinpoint Strike&lt;/color&gt;.
-Không thể nhận Redundant Energy khi đang ở &lt;color=Highlight&gt;Inferno Mode&lt;/color&gt;.</t>
+          <t>Zani có thể chứa tối đa 100 Năng Lượng Dư Thừa.
+Nhận Năng Lượng Dư Thừa khi Normal Attack trúng mục tiêu.
+Nhận Năng Lượng Dư Thừa khi Kỹ Năng Khởi Động &lt;color=Highlight&gt;Thi Hành Ngay Lập Tức&lt;/color&gt; trúng mục tiêu.
+Nhận Năng Lượng Dư Thừa khi sử dụng Resonance Skill &lt;color=Highlight&gt;Giao Thức Phòng Thủ Chuẩn&lt;/color&gt;.
+Nhận Năng Lượng Dư Thừa khi sử dụng Resonance Skill &lt;color=Highlight&gt;Đòn Đánh Chính Xác&lt;/color&gt;.
+Không thể nhận Năng Lượng Dư Thừa khi đang ở &lt;color=Highlight&gt;Chế Độ Hỏa Diệm&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -30105,11 +30105,11 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Blaze bị giới hạn ở mức 100 khi không ở &lt;color=Highlight&gt;Inferno Mode&lt;/color&gt;.
-Blaze bị giới hạn ở mức 150 khi ở &lt;color=Highlight&gt;Inferno Mode&lt;/color&gt;.
-Sử dụng Resonance Skill &lt;color=Highlight&gt;Crisis Response Protocol&lt;/color&gt; sẽ nhận được 10 Blaze.
+          <t>Blaze bị giới hạn ở mức 100 khi không ở &lt;color=Highlight&gt;Chế Độ Hỏa Ngục&lt;/color&gt;.
+Blaze bị giới hạn ở mức 150 khi ở &lt;color=Highlight&gt;Chế Độ Hỏa Ngục&lt;/color&gt;.
+Sử dụng Resonance Skill &lt;color=Highlight&gt;Giao Thức Ứng Phó Khủng Hoảng&lt;/color&gt; sẽ nhận được 10 Blaze.
 Mỗi tầng Heliacal Ember chuyển hóa từ &lt;color=Highlight&gt;Spectro Frazzle&lt;/color&gt; sẽ nhận được 5 Blaze.
-Sử dụng Resonance Liberation &lt;color=Highlight&gt;Rekindle&lt;/color&gt; sẽ nhận được 50 Blaze.</t>
+Sử dụng Resonance Liberation &lt;color=Highlight&gt;Tái Sinh Lửa&lt;/color&gt; sẽ nhận được 50 Blaze.</t>
         </is>
       </c>
     </row>
@@ -30174,7 +30174,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Khi Zani có mặt trong đội và một Resonator gần đó gây &lt;color=Highlight&gt;Spectro Frazzle&lt;/color&gt; lên mục tiêu, ngay lập tức tiêu thụ toàn bộ tầng Spectro Frazzle, kích hoạt sát thương tương ứng, rồi chuyển đổi thành số tầng Heliacal Ember tương đương. Mỗi lần chuyển đổi, Zani nhận được Blaze dựa trên số tầng Heliacal Ember đã gây ra. Heliacal Ember tối đa 60 tầng, mỗi tầng kéo dài 6 giây. Số tầng Heliacal Ember được tính vào tầng Spectro Frazzle cho hiệu ứng Sonata *Eternal Radiance*.</t>
+          <t>Khi Zani có mặt trong đội và một Resonator gần đó gây &lt;color=Highlight&gt;Spectro Frazzle&lt;/color&gt; lên mục tiêu, ngay lập tức tiêu thụ toàn bộ tầng Spectro Frazzle, kích hoạt DMG tương ứng, rồi chuyển đổi thành số tầng Heliacal Ember tương đương. Mỗi lần chuyển đổi, Zani nhận được Blaze dựa trên số tầng Heliacal Ember đã gây ra. Heliacal Ember tối đa 60 tầng, mỗi tầng kéo dài 6 giây. Số tầng Heliacal Ember được tính vào tầng Spectro Frazzle cho hiệu ứng Sonata *Eternal Radiance*.</t>
         </is>
       </c>
     </row>
@@ -30240,8 +30240,8 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Phương pháp này do Tiến sĩ Scott Rabelle phát triển, ban đầu được thiết kế để test Resonators. Nó còn được gọi là "Bài test Rabelle."
-Nổi tiếng với độ an toàn, độ tin cậy và dễ sử dụng, bài test này sau đó đã được áp dụng rộng rãi ở nhiều khu vực.</t>
+          <t>Phương pháp này do Tiến sĩ Scott Rabelle phát triển, ban đầu được thiết kế để kiểm tra Resonator. Nó còn được gọi là "Bài kiểm tra Rabelle."
+Nổi tiếng với độ an toàn, độ tin cậy và dễ sử dụng, bài kiểm tra này sau đó đã được áp dụng rộng rãi ở nhiều khu vực.</t>
         </is>
       </c>
     </row>
@@ -30568,9 +30568,9 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Một dấu hiệu được tìm thấy trên da của Resonators hoặc trên mặt đất của Tacet Field.
-Với Resonators, những dấu hiệu này là đường dẫn cho Forte của họ, biểu tượng cho sự tái sinh sau khi thức tỉnh.
-Trong Tacet Field, dấu hiệu trở thành điểm tập trung năng lượng hỗn loạn, tạo thành Resonance Cord trắng, sinh ra vô số Tacet Discord trên thế giới này.</t>
+          <t>Một dấu hiệu được tìm thấy trên da của Resonator hoặc trên mặt đất của Tổ Tacet.
+Với Resonator, những dấu hiệu này là đường dẫn cho Forte của họ, biểu tượng cho sự tái sinh sau khi thức tỉnh.
+Trong Tổ Tacet, dấu hiệu trở thành điểm tập trung năng lượng hỗn loạn, tạo thành Dây Cộng Hưởng trắng, sinh ra vô số Tacet Discord trên thế giới này.</t>
         </is>
       </c>
     </row>
@@ -30702,7 +30702,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Threnodian là những sinh vật đáng sợ sinh ra từ Nỗi Than Khóc, mang sức mạnh hủy diệt tinh thần con người và nuôi dưỡng bản thân bằng ý chí sụp đổ của họ. Nếu nền văn minh đại diện cho ý chí tập thể của nhân loại, thì Threnodian chính là hiện thân của nỗi sợ hãi và những đấu tranh của chúng ta. Chúng xuất hiện như những thảm họa Discord hủy diệt, lan tràn khắp hành tinh.</t>
+          <t>Threnodian là những sinh vật đáng sợ sinh ra từ Nỗi Than Khóc, mang sức mạnh hủy diệt tinh thần con người và nuôi dưỡng bản thân bằng ý chí sụp đổ của họ. Nếu nền văn minh đại diện cho ý chí tập thể của nhân loại, thì Threnodian chính là hiện thân của nỗi sợ hãi và những đấu tranh của chúng ta. Chúng xuất hiện như những thảm họa Tacet Discord hủy diệt, lan tràn khắp hành tinh.</t>
         </is>
       </c>
     </row>
@@ -30962,7 +30962,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>"Tacet Field" được cho là nơi khởi nguồn của mọi Tacet Discord. Những địa điểm này có bầu trời là biển đảo ngược và một dấu hiệu Tacet hình chữ thập sâu thẳm dưới mặt đất. Âm vang tràn ngập không khí, kết nối thế giới của chúng ta với một không gian bí ẩn thông qua một Sợi Resonance Cord trắng. Những khu vực này thu hút sự tụ tập của các Tacet Discord.</t>
+          <t>"Tổ Tacet" được cho là nơi khởi nguồn của mọi Tacet Discord. Những địa điểm này có bầu trời là biển đảo ngược và một dấu hiệu Tacet hình chữ thập sâu thẳm dưới mặt đất. Âm vang tràn ngập không khí, kết nối thế giới của chúng ta với một không gian bí ẩn thông qua một Sợi Dây Cộng Hưởng trắng. Những khu vực này thu hút sự tụ tập của các Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -31092,7 +31092,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Sức mạnh của Vòng Lặp Tang Tóc gây ra những đợt sóng hủy diệt trên mảnh đất Solaris. Những hiện tượng như "Tacet Field", "Bùng phát Discord" và khoáng vật bí ẩn "Tacetite" đều thuộc nhóm hiện tượng gọi chung là "Hiện tượng Dư Âm".</t>
+          <t>Sức mạnh của Vòng Lặp Tang Tóc gây ra những đợt sóng hủy diệt trên mảnh đất Solaris. Những hiện tượng như "Tổ Tacet", "Bùng phát Tacet Discord" và khoáng vật bí ẩn "Tacetite" đều thuộc nhóm hiện tượng gọi chung là "Hiện tượng Dư Âm".</t>
         </is>
       </c>
     </row>
@@ -31157,7 +31157,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Tacet Discord – những sinh thể được tạo ra từ Waveworn Phenomena, mang trong mình "Lõi Tacet" – là những thực thể nguy hiểm với hình dạng bất định, luôn biến đổi. Chúng hấp thụ các tần số khác để duy trì sự ổn định và tiến hóa, bắt chước khả năng, hình dáng lẫn hành vi của con mồi, tùy thuộc vào loại tần số mà chúng tiêu thụ.</t>
+          <t>Tacet Discord – những sinh thể được tạo ra từ Hiện Tượng Sóng Mòn, mang trong mình "Lõi Tacet" – là những thực thể nguy hiểm với hình dạng bất định, luôn biến đổi. Chúng hấp thụ các tần số khác để duy trì sự ổn định và tiến hóa, bắt chước khả năng, hình dáng lẫn hành vi của con mồi, tùy thuộc vào loại tần số mà chúng tiêu thụ.</t>
         </is>
       </c>
     </row>
@@ -31223,8 +31223,8 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Một loại tần số đặc biệt có thể được Terminal thu thập để tái tạo khả năng của Tacet Discord.
-Khi bị tiêu diệt, Tacet Discord có thể để lại "Dư Âm" với một xác suất nhất định, sau đó được chuyển hóa thành "Echoes" thông qua Data Bank của Terminal, mang lại lợi thế hữu ích trong trận chiến.</t>
+          <t>Một loại tần số đặc biệt có thể được Thiết bị đầu cuối thu thập để tái tạo khả năng của Tacet Discord.
+Khi bị tiêu diệt, Tacet Discord có thể để lại "Dư Âm" với một xác suất nhất định, sau đó được chuyển hóa thành "Echo" thông qua Ngân Hàng Dữ Liệu của Thiết bị đầu cuối, mang lại lợi thế hữu ích trong trận chiến.</t>
         </is>
       </c>
     </row>
@@ -31420,7 +31420,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Ministry of Development đóng vai trò là cánh tay kỹ thuật và xây dựng của Văn Phòng Trung Ương Nhà Nước.
+          <t>Bộ Phát Triển đóng vai trò là cánh tay kỹ thuật và xây dựng của Văn Phòng Trung Ương Nhà Nước.
 Bộ gồm ba phân ban chính: Phòng Vũ Khí và Quốc Phòng, phụ trách mọi ứng dụng quân sự. Và Phòng Cơ Sở Hạ Tầng, đảm nhiệm các dự án công trình công cộng và xây dựng.</t>
         </is>
       </c>
@@ -31486,7 +31486,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Biệt Đội Midnight Rangers là một lực lượng quân sự trực thuộc Ministry of War Jinzhou, do Đại Tướng Jiyan chỉ huy. Họ gồm ba sư đoàn: Kỵ Binh Tiền Trạm (trinh sát), Tiên Phong (tác chiến tấn công) và Hậu Vệ (tác chiến phòng thủ).</t>
+          <t>Biệt Đội Midnight Rangers là một lực lượng quân sự trực thuộc Bộ Chiến Tranh Jinzhou, do Đại Tướng Jiyan chỉ huy. Họ gồm ba sư đoàn: Kỵ Binh Tiền Trạm (trinh sát), Tiên Phong (tác chiến tấn công) và Hậu Vệ (tác chiến phòng thủ).</t>
         </is>
       </c>
     </row>
@@ -31616,7 +31616,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Cơ quan thực thi pháp luật địa phương của Ủy Ban Tư Pháp. Hoạt động thông qua các Patrol Station, đơn vị này duy trì trật tự dân sự và xử lý các vấn đề an ninh công cộng. Các sĩ quan của đơn vị được gọi là "Tuần Tra Viên."</t>
+          <t>Cơ quan thực thi pháp luật địa phương của Ủy Ban Tư Pháp. Hoạt động thông qua các Trạm Tuần Tra, đơn vị này duy trì trật tự dân sự và xử lý các vấn đề an ninh công cộng. Các sĩ quan của đơn vị được gọi là "Tuần Tra Viên."</t>
         </is>
       </c>
     </row>
@@ -31813,7 +31813,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Jinzhou, một thành phố pháo đài ở vùng biên giới, đứng vững trước cuộc khủng hoảng Discord đang đe dọa. Là một trong sáu khu vực lớn của Huanglong, nó gánh vác trách nhiệm này với tư cách là thủ phủ cấp tỉnh trẻ nhất. Đội Midnight Rangers bảo vệ biên giới phía bắc mà không chút do dự.</t>
+          <t>Jinzhou, một thành phố pháo đài ở vùng biên giới, đứng vững trước cuộc khủng hoảng Tacet Discord đang đe dọa. Là một trong sáu khu vực lớn của Huanglong, nó gánh vác trách nhiệm này với tư cách là thủ phủ cấp tỉnh trẻ nhất. Đội Midnight Rangers bảo vệ biên giới phía bắc mà không chút do dự.</t>
         </is>
       </c>
     </row>
@@ -32141,7 +32141,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Một quốc gia gồm các thành bang độc lập nằm rải rác trên quần đảo rộng lớn, không có trung tâm hành chính tập trung. Nơi đây còn được mệnh danh là "Land of Echoes", nổi tiếng với cảnh quan thiên nhiên và văn hóa độc đáo.
+          <t>Một quốc gia gồm các thành bang độc lập nằm rải rác trên quần đảo rộng lớn, không có trung tâm hành chính tập trung. Nơi đây còn được mệnh danh là "Vùng Đất Tiếng Vọng", nổi tiếng với cảnh quan thiên nhiên và văn hóa độc đáo.
 Truyền thuyết kể rằng tổ tiên của Rinascita đã rời bỏ quê hương, vượt biển đến những hòn đảo này để thoát khỏi Lament.</t>
         </is>
       </c>
@@ -32806,7 +32806,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Một Discord khổng lồ hình cá voi. Dù bản tính hiền lành, kích thước đồ sộ của nó vô tình gây ra những tàn phá nghiêm trọng.</t>
+          <t>Một Tacet Discord khổng lồ hình cá voi. Dù bản tính hiền lành, kích thước đồ sộ của nó vô tình gây ra những tàn phá nghiêm trọng.</t>
         </is>
       </c>
     </row>
@@ -33070,7 +33070,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Còn được gọi là Bàn Mô Phỏng Văn Minh, Tethys Hệ thống là siêu máy tính độc nhất của Black Shores. Bằng cách nhập dữ liệu tần số Lament—thu thập thủ công hoặc qua các trạm phát tín hiệu—vào hệ thống, Black Shores có thể đưa ra cảnh báo Lament cho các khu vực trên toàn cầu trong vòng 24 đến 48 giờ. Khả năng này là nền tảng cho sự hợp tác rộng rãi của Black Shores với các quốc gia trên thế giới.</t>
+          <t>Còn được gọi là Bàn Mô Phỏng Văn Minh, Hệ Thống Tethys là siêu máy tính độc nhất của Black Shores. Bằng cách nhập dữ liệu tần số Lament—thu thập thủ công hoặc qua các trạm phát tín hiệu—vào hệ thống, Black Shores có thể đưa ra cảnh báo Lament cho các khu vực trên toàn cầu trong vòng 24 đến 48 giờ. Khả năng này là nền tảng cho sự hợp tác rộng rãi của Black Shores với các quốc gia trên thế giới.</t>
         </is>
       </c>
     </row>
@@ -33137,7 +33137,7 @@
       <c r="M497" t="inlineStr">
         <is>
           <t>Điều biến là quá trình điều chỉnh tần số. Trên Solaris-3, tần số là công cụ tối quan trọng để khám phá chân lý về thực tại. Bằng cách thay đổi những tần số này, ta có thể đi sâu vào cốt lõi của sự tồn tại.
-Tại Black Shores, việc điều biến Ma Trận Sao là bước then chốt để truy vết và phân tích Lament. Suốt lịch sử Black Shores, chỉ duy nhất một cá nhân từng được tôn vinh với danh hiệu "Modulator"—Rover.</t>
+Tại Bờ Biển Đen, việc điều biến Ma Trận Sao là bước then chốt để truy vết và phân tích Lament. Suốt lịch sử Bờ Biển Đen, chỉ duy nhất một cá nhân từng được tôn vinh với danh hiệu "Điều Biến Giả"—Rover.</t>
         </is>
       </c>
     </row>
@@ -33202,7 +33202,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Tuần Tra Ở Jinzhou.</t>
+          <t>Tuần Tra ở Jinzhou.</t>
         </is>
       </c>
     </row>
